--- a/analysis/2025-10-30 Tables for Report.xlsx
+++ b/analysis/2025-10-30 Tables for Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Coach_WAR\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EB18AE-11C4-4A89-93ED-F13A9157D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5990A4C-CFA1-40C9-944A-C2F70303F538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{E7B8E32F-0AEC-4226-BFE4-04A50A9DFAB8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{E7B8E32F-0AEC-4226-BFE4-04A50A9DFAB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Features by Cat" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Top Seasons" sheetId="5" r:id="rId5"/>
     <sheet name="Top Averages" sheetId="6" r:id="rId6"/>
     <sheet name="By Decade" sheetId="7" r:id="rId7"/>
+    <sheet name="Off vs Def" sheetId="8" r:id="rId8"/>
+    <sheet name="Validation" sheetId="9" r:id="rId9"/>
+    <sheet name="Persistence" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Averages'!$H$20:$M$20</definedName>
@@ -67,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="965">
   <si>
     <t>Win_Pct</t>
   </si>
@@ -2640,7 +2643,334 @@
     <t>Delta, 2020's vs. 1970s</t>
   </si>
   <si>
-    <t>Avg. Coach WAR per Season</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test Type                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test Statistic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> p-value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Effect Size        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interpretation             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>---------------------------------</t>
+  </si>
+  <si>
+    <t>----------------</t>
+  </si>
+  <si>
+    <t>--------------------</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Welch's t-test (parametric)     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> t = -1.642     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cohen's d = -0.086 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Not significant            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mann-Whitney U (non-parametric) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U = 260,162    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Background </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Coaches </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Seasons </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mean WAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Median WAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Std Dev </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Offensive  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defensive  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Difference </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -       </t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Marginally significant</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mann-Whitney U test Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Decade </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sample Sizes (O/D)           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mean WAR (O/D)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mann-Whitney U   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cohen's d </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Significance </t>
+  </si>
+  <si>
+    <t>--------</t>
+  </si>
+  <si>
+    <t>------------------------------</t>
+  </si>
+  <si>
+    <t>------------------</t>
+  </si>
+  <si>
+    <t>-----------</t>
+  </si>
+  <si>
+    <t>--------------</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Coaches / Seasons            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> games/season    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> O - D      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U-stat / p-value </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1970s  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -0.355 / +0.573 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3290p = 0.0001   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1980s  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +0.421 / +0.456 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5389p = 0.555    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1990s  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -0.140 / +0.193 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7553p = 0.211    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2000s  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +0.139 / +0.076 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10275p = 0.763   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2010s  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +0.246 / +0.528 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9430p = 0.234    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2020s  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +0.572 / +0.156 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3151p = 0.159    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 38/24 coaches, 95/101 seasons  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 32/19 coaches, 149/76 seasons  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 38/25 coaches, 163/102 seasons </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42/33 coaches, 165/122 seasons </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 44/32 coaches, 163/126 seasons </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 33/22 coaches, 91/61 seasons   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Difference (O - D)</t>
+  </si>
+  <si>
+    <t>U-statistic</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Highly Significant</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Sample Size, Coaches (O/D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validation Strategy          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Training Samples                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test Samples                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Train R² </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test R² </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test RMSE </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generalization Gap </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Temporal Holdout (2020-2024) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Holdout Coaches              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> New Coaches in Modern Era    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1,523 seasons 
+(1970-2019)                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1,363 seasons
+(216 coaches)                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1,652 seasons
+(pre-2020 + 80% of 2020-2024) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 160 seasons
+(2020-2024)                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 320 seasons
+(54 coaches)               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 31 seasons
+(11 new coaches, 2020-2024) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quintile    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Year N WAR (games) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Year N+1 WAR (games) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Change (games) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> % Retained </t>
+  </si>
+  <si>
+    <t>----------------------</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Q1 (Worst)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Q2          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Q3 (Middle) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> N/A        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Q4          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Q5 (Best)   </t>
   </si>
 </sst>
 </file>
@@ -2649,7 +2979,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -2686,15 +3016,21 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -2892,13 +3228,137 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -2909,8 +3369,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2920,8 +3382,10 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="double">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2936,33 +3400,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2971,7 +3409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3098,13 +3536,13 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3122,32 +3560,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3158,23 +3584,170 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3663,6 +4236,268 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD42C9B-D870-448B-8B15-7E5FEE5BEFC2}">
+  <dimension ref="B1:G15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="20"/>
+    <col min="2" max="6" width="17.08984375" style="20" customWidth="1"/>
+    <col min="7" max="8" width="14.90625" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:7" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="51" t="str" cm="1">
+        <f t="array" ref="B2:F2">TRIM(C9:G9)</f>
+        <v>Quintile</v>
+      </c>
+      <c r="C2" s="52" t="str">
+        <v>Year N WAR (games)</v>
+      </c>
+      <c r="D2" s="52" t="str">
+        <v>Year N+1 WAR (games)</v>
+      </c>
+      <c r="E2" s="52" t="str">
+        <v>Change (games)</v>
+      </c>
+      <c r="F2" s="54" t="str">
+        <v>% Retained</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="108" t="str" cm="1">
+        <f t="array" ref="B3:B7">C11:C15</f>
+        <v xml:space="preserve"> Q1 (Worst)  </v>
+      </c>
+      <c r="C3" s="112" cm="1">
+        <f t="array" ref="C3:F7">IFERROR(VALUE(D11:G15),TRIM(D11:G15))</f>
+        <v>-2.33</v>
+      </c>
+      <c r="D3" s="112">
+        <v>-0.93</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1.4</v>
+      </c>
+      <c r="F3" s="45">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B4" s="111" t="str">
+        <v xml:space="preserve"> Q2          </v>
+      </c>
+      <c r="C4" s="113">
+        <v>-0.77</v>
+      </c>
+      <c r="D4" s="113">
+        <v>-0.59</v>
+      </c>
+      <c r="E4" s="114">
+        <v>0.18</v>
+      </c>
+      <c r="F4" s="65">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="111" t="str">
+        <v xml:space="preserve"> Q3 (Middle) </v>
+      </c>
+      <c r="C5" s="113">
+        <v>0.17</v>
+      </c>
+      <c r="D5" s="113">
+        <v>-0.1</v>
+      </c>
+      <c r="E5" s="114">
+        <v>-0.27</v>
+      </c>
+      <c r="F5" s="65" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="109" t="str">
+        <v xml:space="preserve"> Q4          </v>
+      </c>
+      <c r="C6" s="115">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D6" s="115">
+        <v>0.35</v>
+      </c>
+      <c r="E6" s="116">
+        <v>-0.8</v>
+      </c>
+      <c r="F6" s="46">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="110" t="str">
+        <v xml:space="preserve"> Q5 (Best)   </v>
+      </c>
+      <c r="C7" s="117">
+        <v>2.64</v>
+      </c>
+      <c r="D7" s="117">
+        <v>0.65</v>
+      </c>
+      <c r="E7" s="118">
+        <v>-1.99</v>
+      </c>
+      <c r="F7" s="47">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="20" t="s">
+        <v>857</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>953</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>776</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>866</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>958</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>865</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>959</v>
+      </c>
+      <c r="D11" s="119">
+        <v>-2.33</v>
+      </c>
+      <c r="E11" s="119">
+        <v>-0.93</v>
+      </c>
+      <c r="F11" s="120">
+        <v>1.4</v>
+      </c>
+      <c r="G11" s="120">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>960</v>
+      </c>
+      <c r="D12" s="119">
+        <v>-0.77</v>
+      </c>
+      <c r="E12" s="119">
+        <v>-0.59</v>
+      </c>
+      <c r="F12" s="120">
+        <v>0.18</v>
+      </c>
+      <c r="G12" s="120">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>961</v>
+      </c>
+      <c r="D13" s="120">
+        <v>0.17</v>
+      </c>
+      <c r="E13" s="120">
+        <v>-0.1</v>
+      </c>
+      <c r="F13" s="120">
+        <v>-0.27</v>
+      </c>
+      <c r="G13" s="120" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>963</v>
+      </c>
+      <c r="D14" s="120">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E14" s="120">
+        <v>0.35</v>
+      </c>
+      <c r="F14" s="120">
+        <v>-0.8</v>
+      </c>
+      <c r="G14" s="120">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>964</v>
+      </c>
+      <c r="D15" s="120">
+        <v>2.64</v>
+      </c>
+      <c r="E15" s="120">
+        <v>0.65</v>
+      </c>
+      <c r="F15" s="120">
+        <v>-1.99</v>
+      </c>
+      <c r="G15" s="120">
+        <v>0.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129F9831-1725-4379-93CD-2DC6DD2D8C52}">
   <sheetPr codeName="Sheet2"/>
@@ -11778,235 +12613,1242 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A52C07A-37FD-4FD9-80F8-E4D4E39D4100}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="B1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:K32"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="20"/>
-    <col min="2" max="2" width="12.08984375" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" style="57" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="40" customWidth="1"/>
+    <col min="5" max="7" width="14.54296875" style="20" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" style="40" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="16384" width="8.7265625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="88"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2" s="89"/>
+    </row>
+    <row r="3" spans="2:9" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="61" t="s">
+        <v>845</v>
+      </c>
+      <c r="C3" s="23" t="str" cm="1">
+        <f t="array" ref="C3:H3">_xlfn.SEQUENCE(1,6,1970,10)&amp;"'s"</f>
+        <v>1970's</v>
+      </c>
+      <c r="D3" s="23" t="str">
+        <v>1980's</v>
+      </c>
+      <c r="E3" s="23" t="str">
+        <v>1990's</v>
+      </c>
+      <c r="F3" s="23" t="str">
+        <v>2000's</v>
+      </c>
+      <c r="G3" s="23" t="str">
+        <v>2010's</v>
+      </c>
+      <c r="H3" s="24" t="str">
+        <v>2020's</v>
+      </c>
+      <c r="I3" s="54" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="28" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="62" t="s">
+        <v>848</v>
+      </c>
+      <c r="C4" s="64" cm="1">
+        <f t="array" ref="C4:H4">C19:H19</f>
+        <v>-0.35</v>
+      </c>
+      <c r="D4" s="64">
+        <v>0.42</v>
+      </c>
+      <c r="E4" s="64">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="F4" s="64">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G4" s="64">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="45">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I4" s="65">
+        <f t="shared" ref="I4:I6" si="0">H4-C4</f>
+        <v>0.91999999999999993</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="71" t="s">
+        <v>847</v>
+      </c>
+      <c r="C5" s="103" cm="1">
+        <f t="array" ref="C5:H5">C18:H18</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D5" s="103">
+        <v>0.46</v>
+      </c>
+      <c r="E5" s="103">
+        <v>0.19</v>
+      </c>
+      <c r="F5" s="103">
+        <v>0.08</v>
+      </c>
+      <c r="G5" s="103">
+        <v>0.53</v>
+      </c>
+      <c r="H5" s="104">
+        <v>0.16</v>
+      </c>
+      <c r="I5" s="46">
+        <f t="shared" si="0"/>
+        <v>-0.40999999999999992</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="28" hidden="1" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="100" t="s">
+        <v>849</v>
+      </c>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" s="55" customFormat="1" ht="28" customHeight="1" collapsed="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="94" t="s">
+        <v>936</v>
+      </c>
+      <c r="C7" s="90" t="str" cm="1">
+        <f t="array" ref="C7:H7">TRIM(_xlfn.TEXTBEFORE(TRANSPOSE(C27:C32),"coaches"))</f>
+        <v>38/24</v>
+      </c>
+      <c r="D7" s="90" t="str">
+        <v>32/19</v>
+      </c>
+      <c r="E7" s="90" t="str">
+        <v>38/25</v>
+      </c>
+      <c r="F7" s="90" t="str">
+        <v>42/33</v>
+      </c>
+      <c r="G7" s="90" t="str">
+        <v>44/32</v>
+      </c>
+      <c r="H7" s="95" t="str">
+        <v>33/22</v>
+      </c>
+      <c r="I7" s="91"/>
+    </row>
+    <row r="8" spans="2:9" s="55" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="96" t="str">
+        <f>SUBSTITUTE(B7,"Coaches", "Seasons")</f>
+        <v>Sample Size, Seasons (O/D)</v>
+      </c>
+      <c r="C8" s="97" t="str" cm="1">
+        <f t="array" ref="C8:H8">TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(TRANSPOSE(C27:C32),","),"seasons"))</f>
+        <v>95/101</v>
+      </c>
+      <c r="D8" s="97" t="str">
+        <v>149/76</v>
+      </c>
+      <c r="E8" s="97" t="str">
+        <v>163/102</v>
+      </c>
+      <c r="F8" s="97" t="str">
+        <v>165/122</v>
+      </c>
+      <c r="G8" s="97" t="str">
+        <v>163/126</v>
+      </c>
+      <c r="H8" s="98" t="str">
+        <v>91/61</v>
+      </c>
+      <c r="I8" s="99"/>
+    </row>
+    <row r="9" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="78" t="str" cm="1">
+        <f t="array" ref="B9:B10">TRIM(TRANSPOSE(D24:E24))</f>
+        <v>Mean WAR (O/D)</v>
+      </c>
+      <c r="C9" s="32" t="str" cm="1">
+        <f t="array" ref="C9:H10">TRIM(TRANSPOSE(D27:E32))</f>
+        <v>-0.355 / +0.573</v>
+      </c>
+      <c r="D9" s="32" t="str">
+        <v>+0.421 / +0.456</v>
+      </c>
+      <c r="E9" s="32" t="str">
+        <v>-0.140 / +0.193</v>
+      </c>
+      <c r="F9" s="32" t="str">
+        <v>+0.139 / +0.076</v>
+      </c>
+      <c r="G9" s="32" t="str">
+        <v>+0.246 / +0.528</v>
+      </c>
+      <c r="H9" s="34" t="str">
+        <v>+0.572 / +0.156</v>
+      </c>
+      <c r="I9" s="92"/>
+    </row>
+    <row r="10" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="78" t="str">
+        <v>Difference (O - D)</v>
+      </c>
+      <c r="C10" s="32" t="str">
+        <v>-0.927</v>
+      </c>
+      <c r="D10" s="32" t="str">
+        <v>-0.035</v>
+      </c>
+      <c r="E10" s="32" t="str">
+        <v>-0.333</v>
+      </c>
+      <c r="F10" s="32" t="str">
+        <v>0.063</v>
+      </c>
+      <c r="G10" s="32" t="str">
+        <v>-0.282</v>
+      </c>
+      <c r="H10" s="34" t="str">
+        <v>0.416</v>
+      </c>
+      <c r="I10" s="92"/>
+    </row>
+    <row r="11" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="78" t="str" cm="1">
+        <f t="array" ref="B11:B12">TRANSPOSE(J24:K24)</f>
+        <v>U-statistic</v>
+      </c>
+      <c r="C11" s="32" cm="1">
+        <f t="array" ref="C11:H12">TRANSPOSE(J27:K32)</f>
+        <v>3290</v>
+      </c>
+      <c r="D11" s="32">
+        <v>5389</v>
+      </c>
+      <c r="E11" s="32">
+        <v>7553</v>
+      </c>
+      <c r="F11" s="32">
+        <v>10275</v>
+      </c>
+      <c r="G11" s="32">
+        <v>9430</v>
+      </c>
+      <c r="H11" s="34">
+        <v>3151</v>
+      </c>
+      <c r="I11" s="92"/>
+    </row>
+    <row r="12" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="78" t="str">
+        <v>p-value</v>
+      </c>
+      <c r="C12" s="32">
+        <v>1E-4</v>
+      </c>
+      <c r="D12" s="32">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="E12" s="32">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="F12" s="32">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="G12" s="32">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="H12" s="34">
+        <v>0.159</v>
+      </c>
+      <c r="I12" s="92"/>
+    </row>
+    <row r="13" spans="2:9" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="83" t="str">
+        <f>TRIM(H24)</f>
+        <v>Significance</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>934</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>935</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>935</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>935</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>935</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>935</v>
+      </c>
+      <c r="I13" s="93"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="20" t="s">
+        <v>846</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>850</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>851</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>852</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>853</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>854</v>
+      </c>
+      <c r="H16" s="40" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B17" s="20" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B18" s="20" t="s">
+        <v>847</v>
+      </c>
+      <c r="C18" s="57">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D18" s="40">
+        <v>0.46</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0.19</v>
+      </c>
+      <c r="F18" s="20">
+        <v>0.08</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0.53</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B19" s="20" t="s">
+        <v>848</v>
+      </c>
+      <c r="C19" s="57">
+        <v>-0.35</v>
+      </c>
+      <c r="D19" s="40">
+        <v>0.42</v>
+      </c>
+      <c r="E19" s="20">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="F19" s="20">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G19" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B20" s="20" t="s">
+        <v>849</v>
+      </c>
+      <c r="C20" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="D20" s="40">
+        <v>-0.11</v>
+      </c>
+      <c r="E20" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="F20" s="20">
+        <v>0.04</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0.43</v>
+      </c>
+      <c r="H20" s="40">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" s="55" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="B24" s="67" t="s">
+        <v>887</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>888</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>889</v>
+      </c>
+      <c r="E24" s="55" t="s">
+        <v>931</v>
+      </c>
+      <c r="F24" s="55" t="s">
+        <v>890</v>
+      </c>
+      <c r="G24" s="68" t="s">
+        <v>891</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>892</v>
+      </c>
+      <c r="I24" s="68"/>
+      <c r="J24" s="55" t="s">
+        <v>932</v>
+      </c>
+      <c r="K24" s="55" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B25" s="57" t="s">
+        <v>893</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>894</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>778</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>895</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>896</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B26" s="57" t="s">
+        <v>898</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>899</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>900</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>901</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>902</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>903</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B27" s="57" t="s">
+        <v>905</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>925</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>906</v>
+      </c>
+      <c r="E27" s="20">
+        <v>-0.92700000000000005</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>907</v>
+      </c>
+      <c r="G27" s="40">
+        <v>-0.53200000000000003</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>908</v>
+      </c>
+      <c r="J27" s="20" cm="1">
+        <f t="array" ref="J27:J32">VALUE(_xlfn.TEXTBEFORE(F27:F32,"p"))</f>
+        <v>3290</v>
+      </c>
+      <c r="K27" s="20" cm="1">
+        <f t="array" ref="K27:K32">VALUE(_xlfn.TEXTAFTER(F27:F32,"="))</f>
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B28" s="57" t="s">
+        <v>909</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>926</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="E28" s="20">
+        <v>-3.5000000000000003E-2</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>911</v>
+      </c>
+      <c r="G28" s="40">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>912</v>
+      </c>
+      <c r="J28" s="20">
+        <v>5389</v>
+      </c>
+      <c r="K28" s="20">
+        <v>0.55500000000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B29" s="57" t="s">
+        <v>913</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>927</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>914</v>
+      </c>
+      <c r="E29" s="20">
+        <v>-0.33300000000000002</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="G29" s="40">
+        <v>-0.17399999999999999</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>912</v>
+      </c>
+      <c r="J29" s="20">
+        <v>7553</v>
+      </c>
+      <c r="K29" s="20">
+        <v>0.21099999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B30" s="57" t="s">
+        <v>916</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>928</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="E30" s="20">
+        <v>6.3E-2</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>918</v>
+      </c>
+      <c r="G30" s="40">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>912</v>
+      </c>
+      <c r="J30" s="20">
+        <v>10275</v>
+      </c>
+      <c r="K30" s="20">
+        <v>0.76300000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B31" s="57" t="s">
+        <v>919</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>929</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>920</v>
+      </c>
+      <c r="E31" s="20">
+        <v>-0.28199999999999997</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>921</v>
+      </c>
+      <c r="G31" s="40">
+        <v>-0.151</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>912</v>
+      </c>
+      <c r="J31" s="20">
+        <v>9430</v>
+      </c>
+      <c r="K31" s="20">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B32" s="57" t="s">
+        <v>922</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>930</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>923</v>
+      </c>
+      <c r="E32" s="20">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>924</v>
+      </c>
+      <c r="G32" s="40">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>912</v>
+      </c>
+      <c r="J32" s="20">
+        <v>3151</v>
+      </c>
+      <c r="K32" s="20">
+        <v>0.159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A2CB53-2941-4642-9382-91358B7FAA54}">
+  <dimension ref="B2:I26"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="20"/>
+    <col min="2" max="2" width="13" style="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" style="57" customWidth="1"/>
     <col min="4" max="4" width="9.08984375" style="40" customWidth="1"/>
     <col min="5" max="7" width="9.08984375" style="20" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" style="40" customWidth="1"/>
+    <col min="8" max="8" width="19.453125" style="40" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6328125" style="40" customWidth="1"/>
     <col min="10" max="16384" width="8.7265625" style="20"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+    </row>
+    <row r="3" spans="2:9" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="66" t="s">
+        <v>845</v>
+      </c>
+      <c r="C3" s="52" t="str" cm="1">
+        <f t="array" ref="C3:G3">D16:H16</f>
+        <v xml:space="preserve"> Coaches </v>
+      </c>
+      <c r="D3" s="52" t="str">
+        <v xml:space="preserve"> Seasons </v>
+      </c>
+      <c r="E3" s="52" t="str">
+        <v xml:space="preserve"> Mean WAR </v>
+      </c>
+      <c r="F3" s="52" t="str">
+        <v xml:space="preserve"> Median WAR </v>
+      </c>
+      <c r="G3" s="72" t="str">
+        <v xml:space="preserve"> Std Dev </v>
+      </c>
+      <c r="H3" s="75" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="62" t="s">
+        <v>847</v>
+      </c>
+      <c r="C4" s="69" cm="1">
+        <f t="array" ref="C4:G4">D19:H19</f>
+        <v>112</v>
+      </c>
+      <c r="D4" s="69">
+        <v>639</v>
+      </c>
+      <c r="E4" s="28">
+        <v>1.52E-2</v>
+      </c>
+      <c r="F4" s="28">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G4" s="73">
+        <v>0.1111</v>
+      </c>
+      <c r="H4" s="76"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="63" t="s">
+        <v>848</v>
+      </c>
+      <c r="C5" s="70" cm="1">
+        <f t="array" ref="C5:G5">D18:H18</f>
+        <v>154</v>
+      </c>
+      <c r="D5" s="70">
+        <v>860</v>
+      </c>
+      <c r="E5" s="33">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="F5" s="33">
+        <v>2.3E-3</v>
+      </c>
+      <c r="G5" s="74">
+        <v>0.1134</v>
+      </c>
+      <c r="H5" s="77"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="63" t="s">
+        <v>884</v>
+      </c>
+      <c r="C6" s="70" cm="1">
+        <f t="array" ref="C6:G6">_xlfn.ANCHORARRAY(C5)-_xlfn.ANCHORARRAY(C4)</f>
+        <v>42</v>
+      </c>
+      <c r="D6" s="70">
+        <v>221</v>
+      </c>
+      <c r="E6" s="33">
+        <v>-9.7000000000000003E-3</v>
+      </c>
+      <c r="F6" s="33">
+        <v>-1.6199999999999999E-2</v>
+      </c>
+      <c r="G6" s="74">
+        <v>2.2999999999999965E-3</v>
+      </c>
+      <c r="H6" s="77"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="78" t="str" cm="1">
+        <f t="array" ref="B7:B10">TRIM(TRANSPOSE(D23:G23))</f>
+        <v>Test Statistic</v>
+      </c>
+      <c r="C7" s="79"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="34" t="str" cm="1">
+        <f t="array" ref="H7:H10">TRIM(TRANSPOSE(D26:G26))</f>
+        <v>U = 260,162</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="78" t="str">
+        <v>p-value</v>
+      </c>
+      <c r="C8" s="79"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="34" t="str">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="78" t="str">
+        <v>Effect Size</v>
+      </c>
+      <c r="C9" s="79"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="34" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="83" t="str">
+        <v>Interpretation</v>
+      </c>
+      <c r="C10" s="84"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="39" t="str">
+        <v>Marginally significant</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" s="55" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="55" t="s">
+        <v>863</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>874</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>875</v>
+      </c>
+      <c r="E16" s="55" t="s">
+        <v>876</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>877</v>
+      </c>
+      <c r="G16" s="55" t="s">
+        <v>878</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>879</v>
+      </c>
+      <c r="I16" s="68"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B17" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>795</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>775</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>775</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>807</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B18" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>880</v>
+      </c>
+      <c r="D18" s="40">
+        <v>154</v>
+      </c>
+      <c r="E18" s="20">
+        <v>860</v>
+      </c>
+      <c r="F18" s="20">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="G18" s="20">
+        <v>2.3E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.1134</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B19" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>881</v>
+      </c>
+      <c r="D19" s="40">
+        <v>112</v>
+      </c>
+      <c r="E19" s="20">
+        <v>639</v>
+      </c>
+      <c r="F19" s="20">
+        <v>1.52E-2</v>
+      </c>
+      <c r="G19" s="20">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.1111</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B20" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>882</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>883</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>883</v>
+      </c>
+      <c r="F20" s="20">
+        <v>-9.5999999999999992E-3</v>
+      </c>
+      <c r="G20" s="20">
+        <v>-1.6199999999999999E-2</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" s="55" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="55" t="s">
+        <v>857</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>858</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>859</v>
+      </c>
+      <c r="E23" s="55" t="s">
+        <v>860</v>
+      </c>
+      <c r="F23" s="55" t="s">
+        <v>861</v>
+      </c>
+      <c r="G23" s="55" t="s">
+        <v>862</v>
+      </c>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>864</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>865</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>775</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>866</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B25" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C25" s="57" t="s">
+        <v>867</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>868</v>
+      </c>
+      <c r="E25" s="20">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B26" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C26" s="57" t="s">
+        <v>871</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>872</v>
+      </c>
+      <c r="E26" s="20">
+        <v>7.8E-2</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>873</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>885</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A65AF39-4FCA-4ECA-9A3F-8206E401F864}">
+  <dimension ref="B1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="20"/>
+    <col min="2" max="2" width="19.36328125" style="20" customWidth="1"/>
+    <col min="3" max="4" width="21.08984375" style="20" customWidth="1"/>
+    <col min="5" max="8" width="14.90625" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="20"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="63" t="s">
-        <v>857</v>
-      </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="64"/>
-      <c r="I2"/>
-    </row>
-    <row r="3" spans="2:9" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="65" t="s">
-        <v>845</v>
-      </c>
-      <c r="C3" s="61" t="str" cm="1">
-        <f t="array" ref="C3:H3">_xlfn.SEQUENCE(1,6,1970,10)&amp;"'s"</f>
-        <v>1970's</v>
-      </c>
-      <c r="D3" s="61" t="str">
-        <v>1980's</v>
-      </c>
-      <c r="E3" s="61" t="str">
-        <v>1990's</v>
-      </c>
-      <c r="F3" s="61" t="str">
-        <v>2000's</v>
-      </c>
-      <c r="G3" s="61" t="str">
-        <v>2010's</v>
-      </c>
-      <c r="H3" s="62" t="str">
-        <v>2020's</v>
-      </c>
-      <c r="I3" s="73" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="66" t="s">
-        <v>847</v>
-      </c>
-      <c r="C4" s="69" cm="1">
-        <f t="array" ref="C4:H6">C11:H13</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="D4" s="69">
-        <v>0.46</v>
-      </c>
-      <c r="E4" s="69">
-        <v>0.19</v>
-      </c>
-      <c r="F4" s="69">
-        <v>0.08</v>
-      </c>
-      <c r="G4" s="69">
-        <v>0.53</v>
-      </c>
-      <c r="H4" s="45">
-        <v>0.16</v>
-      </c>
-      <c r="I4" s="72">
-        <f t="shared" ref="I4:I6" si="0">H4-C4</f>
-        <v>-0.40999999999999992</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B5" s="67" t="s">
-        <v>848</v>
-      </c>
-      <c r="C5" s="70">
-        <v>-0.35</v>
-      </c>
-      <c r="D5" s="70">
-        <v>0.42</v>
-      </c>
-      <c r="E5" s="70">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="F5" s="70">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G5" s="70">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="46">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="I5" s="46">
-        <f t="shared" si="0"/>
-        <v>0.91999999999999993</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="68" t="s">
-        <v>849</v>
-      </c>
-      <c r="C6" s="71">
-        <v>0.02</v>
-      </c>
-      <c r="D6" s="71">
-        <v>-0.11</v>
-      </c>
-      <c r="E6" s="71">
-        <v>0.51</v>
-      </c>
-      <c r="F6" s="71">
-        <v>0.04</v>
-      </c>
-      <c r="G6" s="71">
-        <v>0.43</v>
-      </c>
-      <c r="H6" s="47">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-      <c r="I6" s="47">
-        <f t="shared" si="0"/>
-        <v>-9.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="51" t="str" cm="1">
+        <f t="array" ref="B2:H5">TRIM(C7:I10)</f>
+        <v>Validation Strategy</v>
+      </c>
+      <c r="C2" s="52" t="str">
+        <v>Training Samples</v>
+      </c>
+      <c r="D2" s="52" t="str">
+        <v>Test Samples</v>
+      </c>
+      <c r="E2" s="52" t="str">
+        <v>Train R²</v>
+      </c>
+      <c r="F2" s="52" t="str">
+        <v>Test R²</v>
+      </c>
+      <c r="G2" s="52" t="str">
+        <v>Test RMSE</v>
+      </c>
+      <c r="H2" s="54" t="str">
+        <v>Generalization Gap</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="28.5" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="108" t="str">
+        <v>Temporal Holdout (2020-2024)</v>
+      </c>
+      <c r="C3" s="105" t="str">
+        <v>1,523 seasons 
+(1970-2019)</v>
+      </c>
+      <c r="D3" s="105" t="str">
+        <v>160 seasons
+(2020-2024)</v>
+      </c>
+      <c r="E3" s="27" t="str">
+        <v>0.824</v>
+      </c>
+      <c r="F3" s="28" t="str">
+        <v>0.731</v>
+      </c>
+      <c r="G3" s="28" t="str">
+        <v>0.098</v>
+      </c>
+      <c r="H3" s="29" t="str">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="B4" s="109" t="str">
+        <v>Holdout Coaches</v>
+      </c>
+      <c r="C4" s="106" t="str">
+        <v>1,363 seasons
+(216 coaches)</v>
+      </c>
+      <c r="D4" s="106" t="str">
+        <v>320 seasons
+(54 coaches)</v>
+      </c>
+      <c r="E4" s="32" t="str">
+        <v>0.816</v>
+      </c>
+      <c r="F4" s="33" t="str">
+        <v>0.745</v>
+      </c>
+      <c r="G4" s="33" t="str">
+        <v>0.097</v>
+      </c>
+      <c r="H4" s="34" t="str">
+        <v>0.071</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="110" t="str">
+        <v>New Coaches in Modern Era</v>
+      </c>
+      <c r="C5" s="107" t="str">
+        <v>1,652 seasons
+(pre-2020 + 80% of 2020-2024)</v>
+      </c>
+      <c r="D5" s="107" t="str">
+        <v>31 seasons
+(11 new coaches, 2020-2024)</v>
+      </c>
+      <c r="E5" s="37" t="str">
+        <v>0.811</v>
+      </c>
+      <c r="F5" s="38" t="str">
+        <v>0.771</v>
+      </c>
+      <c r="G5" s="38" t="str">
+        <v>0.093</v>
+      </c>
+      <c r="H5" s="39" t="str">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C7" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>938</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>939</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>940</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>941</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>942</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B8" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>944</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>947</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>950</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="H8" s="20">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="I8" s="20">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
-        <v>846</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>850</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>851</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>852</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>854</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+        <v>863</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>948</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>951</v>
+      </c>
+      <c r="F9" s="20">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0.745</v>
+      </c>
+      <c r="H9" s="20">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="I9" s="20">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B11" s="20" t="s">
-        <v>847</v>
-      </c>
-      <c r="C11" s="57">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="D11" s="40">
-        <v>0.46</v>
-      </c>
-      <c r="E11" s="20">
-        <v>0.19</v>
-      </c>
-      <c r="F11" s="20">
-        <v>0.08</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0.53</v>
-      </c>
-      <c r="H11" s="40">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="20" t="s">
-        <v>848</v>
-      </c>
-      <c r="C12" s="57">
-        <v>-0.35</v>
-      </c>
-      <c r="D12" s="40">
-        <v>0.42</v>
-      </c>
-      <c r="E12" s="20">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="F12" s="20">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G12" s="20">
-        <v>0.25</v>
-      </c>
-      <c r="H12" s="40">
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B13" s="20" t="s">
-        <v>849</v>
-      </c>
-      <c r="C13" s="57">
-        <v>0.02</v>
-      </c>
-      <c r="D13" s="40">
-        <v>-0.11</v>
-      </c>
-      <c r="E13" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="F13" s="20">
-        <v>0.04</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0.43</v>
-      </c>
-      <c r="H13" s="40">
-        <v>-7.0000000000000007E-2</v>
+        <v>863</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>946</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>949</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>952</v>
+      </c>
+      <c r="F10" s="20">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="G10" s="20">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="H10" s="20">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="I10" s="20">
+        <v>4.1000000000000002E-2</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/2025-10-30 Tables for Report.xlsx
+++ b/analysis/2025-10-30 Tables for Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Coach_WAR\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5990A4C-CFA1-40C9-944A-C2F70303F538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597BA269-3806-4D62-88E7-C3990F838C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{E7B8E32F-0AEC-4226-BFE4-04A50A9DFAB8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{E7B8E32F-0AEC-4226-BFE4-04A50A9DFAB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Features by Cat" sheetId="2" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="997">
   <si>
     <t>Win_Pct</t>
   </si>
@@ -2496,15 +2496,9 @@
     <t>----------</t>
   </si>
   <si>
-    <t>Jim Mora Sr</t>
-  </si>
-  <si>
     <t>DET</t>
   </si>
   <si>
-    <t>Marty Mornhinweg</t>
-  </si>
-  <si>
     <t>Ron Meyer</t>
   </si>
   <si>
@@ -2514,30 +2508,15 @@
     <t>Matt Eberflus</t>
   </si>
   <si>
-    <t>Mike Riley</t>
-  </si>
-  <si>
     <t>Dan Campbell</t>
   </si>
   <si>
-    <t>CAR</t>
-  </si>
-  <si>
-    <t>George Seifert</t>
-  </si>
-  <si>
     <t>Steve Spagnuolo</t>
   </si>
   <si>
-    <t>NWE</t>
-  </si>
-  <si>
     <t>Bill Belichick</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
     <t>SFO</t>
   </si>
   <si>
@@ -2556,12 +2535,6 @@
     <t>Dan Quinn</t>
   </si>
   <si>
-    <t>Joe Bugel</t>
-  </si>
-  <si>
-    <t>Norv Turner</t>
-  </si>
-  <si>
     <t>Mike Martz</t>
   </si>
   <si>
@@ -2577,15 +2550,9 @@
     <t>Number of Seasons</t>
   </si>
   <si>
-    <t>Dan Henning</t>
-  </si>
-  <si>
     <t>Kay Stephenson</t>
   </si>
   <si>
-    <t>Mike McCormack</t>
-  </si>
-  <si>
     <t>Abe Gibron</t>
   </si>
   <si>
@@ -2646,88 +2613,16 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve"> Test Type                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Test Statistic </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> p-value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Effect Size        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Interpretation             </t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t>---------------------------------</t>
-  </si>
-  <si>
     <t>----------------</t>
   </si>
   <si>
     <t>--------------------</t>
   </si>
   <si>
-    <t xml:space="preserve"> Welch's t-test (parametric)     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> t = -1.642     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cohen's d = -0.086 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Not significant            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mann-Whitney U (non-parametric) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> U = 260,162    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Background </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Coaches </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Seasons </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mean WAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Median WAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Std Dev </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Offensive  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Defensive  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Difference </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -       </t>
-  </si>
-  <si>
     <t>Difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Marginally significant</t>
   </si>
   <si>
     <t xml:space="preserve"> Mann-Whitney U test Value</t>
@@ -2971,6 +2866,207 @@
   </si>
   <si>
     <t xml:space="preserve"> Q5 (Best)   </t>
+  </si>
+  <si>
+    <t>NYG</t>
+  </si>
+  <si>
+    <t>Bill Parcells</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>Bill Cowher</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Jerry Williams</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>David Shula</t>
+  </si>
+  <si>
+    <t>HTX</t>
+  </si>
+  <si>
+    <t>Bill O'Brien</t>
+  </si>
+  <si>
+    <t>Don McCafferty</t>
+  </si>
+  <si>
+    <t>Rick Forzano</t>
+  </si>
+  <si>
+    <t>Paul Brown</t>
+  </si>
+  <si>
+    <t>-------------------------------</t>
+  </si>
+  <si>
+    <t>---------------</t>
+  </si>
+  <si>
+    <t>Mike Vrabel</t>
+  </si>
+  <si>
+    <t>Bill Arnsparger</t>
+  </si>
+  <si>
+    <t>Hue Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Size, Coaches (O/D)    38/24    32/19    38/25    42/33    44/32    33/22    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Size, Seasons (O/D)    95/102    149/76    163/102    165/122    163/126    91/61    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean WAR (O/D)                 -0.453 / +0.602    +0.441 / +0.368    -0.187 / +0.235    +0.056 / +0.091    +0.048 / +0.369    +0.434 / +0.059    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference (O - D)             -1.055    +0.073    -0.422    -0.034    -0.321    +0.375    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-statistic                    3351    5488    7392    9989    9283    3080    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p-value                        0.0002    0.7071    0.1294    0.9135    0.1619    0.2532    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Significance                   Highly Significant    -    -    -    -    -    </t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Size,</t>
+  </si>
+  <si>
+    <t>Coaches</t>
+  </si>
+  <si>
+    <t>(O/D)</t>
+  </si>
+  <si>
+    <t>34/21</t>
+  </si>
+  <si>
+    <t>30/22</t>
+  </si>
+  <si>
+    <t>33/28</t>
+  </si>
+  <si>
+    <t>40/37</t>
+  </si>
+  <si>
+    <t>42/33</t>
+  </si>
+  <si>
+    <t>33/20</t>
+  </si>
+  <si>
+    <t>87/82</t>
+  </si>
+  <si>
+    <t>146/83</t>
+  </si>
+  <si>
+    <t>143/126</t>
+  </si>
+  <si>
+    <t>152/151</t>
+  </si>
+  <si>
+    <t>158/135</t>
+  </si>
+  <si>
+    <t>92/56</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>(O</t>
+  </si>
+  <si>
+    <t>D)</t>
+  </si>
+  <si>
+    <t>Significance</t>
+  </si>
+  <si>
+    <t>Highly</t>
+  </si>
+  <si>
+    <t>Significant</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Std</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Mean WAR</t>
+  </si>
+  <si>
+    <t>Median WAR</t>
+  </si>
+  <si>
+    <t>Std Dev</t>
+  </si>
+  <si>
+    <t>---------------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>games</t>
+  </si>
+  <si>
+    <t>Mann-Whitney</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>(All</t>
+  </si>
+  <si>
+    <t>Seasons):</t>
+  </si>
+  <si>
+    <t>U-statistic:</t>
+  </si>
+  <si>
+    <t>p-value:</t>
+  </si>
+  <si>
+    <t>Interpretation:</t>
+  </si>
+  <si>
+    <t>Marginally</t>
+  </si>
+  <si>
+    <t>significant</t>
   </si>
 </sst>
 </file>
@@ -3030,7 +3126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -3239,45 +3335,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="double">
         <color indexed="64"/>
@@ -3405,11 +3462,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3560,9 +3701,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3605,19 +3743,10 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3634,7 +3763,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3649,17 +3778,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3668,16 +3797,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3693,12 +3822,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3719,16 +3842,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3747,6 +3870,48 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4267,18 +4432,18 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="108" t="str" cm="1">
+      <c r="B3" s="102" t="str" cm="1">
         <f t="array" ref="B3:B7">C11:C15</f>
         <v xml:space="preserve"> Q1 (Worst)  </v>
       </c>
-      <c r="C3" s="112" cm="1">
+      <c r="C3" s="106" cm="1">
         <f t="array" ref="C3:F7">IFERROR(VALUE(D11:G15),TRIM(D11:G15))</f>
         <v>-2.33</v>
       </c>
-      <c r="D3" s="112">
+      <c r="D3" s="106">
         <v>-0.93</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="63">
         <v>1.4</v>
       </c>
       <c r="F3" s="45">
@@ -4286,50 +4451,50 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B4" s="111" t="str">
+      <c r="B4" s="105" t="str">
         <v xml:space="preserve"> Q2          </v>
       </c>
-      <c r="C4" s="113">
+      <c r="C4" s="107">
         <v>-0.77</v>
       </c>
-      <c r="D4" s="113">
+      <c r="D4" s="107">
         <v>-0.59</v>
       </c>
-      <c r="E4" s="114">
+      <c r="E4" s="108">
         <v>0.18</v>
       </c>
-      <c r="F4" s="65">
+      <c r="F4" s="64">
         <v>0.77</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B5" s="111" t="str">
+      <c r="B5" s="105" t="str">
         <v xml:space="preserve"> Q3 (Middle) </v>
       </c>
-      <c r="C5" s="113">
+      <c r="C5" s="107">
         <v>0.17</v>
       </c>
-      <c r="D5" s="113">
+      <c r="D5" s="107">
         <v>-0.1</v>
       </c>
-      <c r="E5" s="114">
+      <c r="E5" s="108">
         <v>-0.27</v>
       </c>
-      <c r="F5" s="65" t="str">
+      <c r="F5" s="64" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="109" t="str">
+      <c r="B6" s="103" t="str">
         <v xml:space="preserve"> Q4          </v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6" s="109">
         <v>1.1499999999999999</v>
       </c>
-      <c r="D6" s="115">
+      <c r="D6" s="109">
         <v>0.35</v>
       </c>
-      <c r="E6" s="116">
+      <c r="E6" s="110">
         <v>-0.8</v>
       </c>
       <c r="F6" s="46">
@@ -4337,16 +4502,16 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="110" t="str">
+      <c r="B7" s="104" t="str">
         <v xml:space="preserve"> Q5 (Best)   </v>
       </c>
-      <c r="C7" s="117">
+      <c r="C7" s="111">
         <v>2.64</v>
       </c>
-      <c r="D7" s="117">
+      <c r="D7" s="111">
         <v>0.65</v>
       </c>
-      <c r="E7" s="118">
+      <c r="E7" s="112">
         <v>-1.99</v>
       </c>
       <c r="F7" s="47">
@@ -4355,39 +4520,39 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>953</v>
+        <v>918</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>954</v>
+        <v>919</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>956</v>
+        <v>921</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>957</v>
+        <v>922</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>776</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>958</v>
+        <v>923</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>865</v>
+        <v>848</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>795</v>
@@ -4395,101 +4560,101 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>959</v>
-      </c>
-      <c r="D11" s="119">
+        <v>924</v>
+      </c>
+      <c r="D11" s="113">
         <v>-2.33</v>
       </c>
-      <c r="E11" s="119">
+      <c r="E11" s="113">
         <v>-0.93</v>
       </c>
-      <c r="F11" s="120">
+      <c r="F11" s="114">
         <v>1.4</v>
       </c>
-      <c r="G11" s="120">
+      <c r="G11" s="114">
         <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>960</v>
-      </c>
-      <c r="D12" s="119">
+        <v>925</v>
+      </c>
+      <c r="D12" s="113">
         <v>-0.77</v>
       </c>
-      <c r="E12" s="119">
+      <c r="E12" s="113">
         <v>-0.59</v>
       </c>
-      <c r="F12" s="120">
+      <c r="F12" s="114">
         <v>0.18</v>
       </c>
-      <c r="G12" s="120">
+      <c r="G12" s="114">
         <v>0.77</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>961</v>
-      </c>
-      <c r="D13" s="120">
+        <v>926</v>
+      </c>
+      <c r="D13" s="114">
         <v>0.17</v>
       </c>
-      <c r="E13" s="120">
+      <c r="E13" s="114">
         <v>-0.1</v>
       </c>
-      <c r="F13" s="120">
+      <c r="F13" s="114">
         <v>-0.27</v>
       </c>
-      <c r="G13" s="120" t="s">
-        <v>962</v>
+      <c r="G13" s="114" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>963</v>
-      </c>
-      <c r="D14" s="120">
+        <v>928</v>
+      </c>
+      <c r="D14" s="114">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E14" s="120">
+      <c r="E14" s="114">
         <v>0.35</v>
       </c>
-      <c r="F14" s="120">
+      <c r="F14" s="114">
         <v>-0.8</v>
       </c>
-      <c r="G14" s="120">
+      <c r="G14" s="114">
         <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>964</v>
-      </c>
-      <c r="D15" s="120">
+        <v>929</v>
+      </c>
+      <c r="D15" s="114">
         <v>2.64</v>
       </c>
-      <c r="E15" s="120">
+      <c r="E15" s="114">
         <v>0.65</v>
       </c>
-      <c r="F15" s="120">
+      <c r="F15" s="114">
         <v>-1.99</v>
       </c>
-      <c r="G15" s="120">
+      <c r="G15" s="114">
         <v>0.25</v>
       </c>
     </row>
@@ -9686,108 +9851,107 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF79A6B8-94D2-472B-99F2-206A2704EBA3}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B1:C14"/>
+  <dimension ref="B2:C14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="120" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="121" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="122" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="124">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="124">
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="4">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
+      <c r="C6" s="124">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B7" s="123" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="124">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="123" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="124">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B9" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
+      <c r="C9" s="124">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B10" s="123" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="124">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B11" s="123" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
+      <c r="C11" s="125">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B12" s="123" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
+      <c r="C12" s="125">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B13" s="123" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="4">
-        <v>8</v>
+      <c r="C13" s="124">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.35">
@@ -9841,22 +10005,22 @@
       </c>
       <c r="C3" s="26" t="str" cm="1">
         <f t="array" ref="C3:C22">C26:C45</f>
-        <v>1stD__opp__hc_Norm</v>
+        <v>ReservesIR/PUP/NFI/SUSP_Pct</v>
       </c>
       <c r="D3" s="27" cm="1">
         <f t="array" ref="D3:D22">INDEX(Features!$B$3:$B$370,MATCH($C$3:$C$22,Features!$C$3:$C$370,0))</f>
-        <v>339</v>
+        <v>6</v>
       </c>
       <c r="E3" s="26" t="str" cm="1">
         <f t="array" ref="E3:E22">INDEX(Features!$E$3:$E$370,MATCH($C$3:$C$22,Features!$C$3:$C$370,0))</f>
-        <v>Normalized first downs allowed under HC</v>
+        <v>Reserve/injured/suspended cap as percentage of maximum</v>
       </c>
       <c r="F3" s="28" cm="1">
         <f t="array" ref="F3:G22">IF(D26:E45="","",D26:E45)</f>
-        <v>5.0374000000000002E-2</v>
+        <v>2.2554999999999999E-2</v>
       </c>
       <c r="G3" s="29" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
@@ -9864,16 +10028,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="31" t="str">
-        <v>Opp_Int_Passing_Norm</v>
+        <v>Team_Int_Passing_Norm</v>
       </c>
       <c r="D4" s="32">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E4" s="31" t="str">
-        <v>Normalized opponent interceptions thrown</v>
+        <v>Normalized team interceptions thrown</v>
       </c>
       <c r="F4" s="33">
-        <v>3.2133000000000002E-2</v>
+        <v>1.4893999999999999E-2</v>
       </c>
       <c r="G4" s="34" t="str">
         <v/>
@@ -9884,19 +10048,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="31" t="str">
-        <v>Yds__opp__hc_Norm</v>
+        <v>Opp_Int_Passing_Norm</v>
       </c>
       <c r="D5" s="32">
-        <v>336</v>
+        <v>196</v>
       </c>
       <c r="E5" s="31" t="str">
-        <v>Normalized yards allowed under HC</v>
+        <v>Normalized opponent interceptions thrown</v>
       </c>
       <c r="F5" s="33">
-        <v>2.7653E-2</v>
+        <v>1.4399E-2</v>
       </c>
       <c r="G5" s="34" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -9904,16 +10068,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="31" t="str">
-        <v>Team_Int_Passing_Norm</v>
+        <v>QB_Max_Games_Missed_Pct</v>
       </c>
       <c r="D6" s="32">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="E6" s="31" t="str">
-        <v>Normalized team interceptions thrown</v>
+        <v>Maximum percentage of games missed by a QB</v>
       </c>
       <c r="F6" s="33">
-        <v>2.7071000000000001E-2</v>
+        <v>1.2807000000000001E-2</v>
       </c>
       <c r="G6" s="34" t="str">
         <v/>
@@ -9924,19 +10088,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="31" t="str">
-        <v>ReservesIR/PUP/NFI/SUSP_Pct</v>
+        <v>PF (Points For)__hc_Norm</v>
       </c>
       <c r="D7" s="32">
-        <v>6</v>
+        <v>302</v>
       </c>
       <c r="E7" s="31" t="str">
-        <v>Reserve/injured/suspended cap as percentage of maximum</v>
+        <v>Normalized points scored under HC</v>
       </c>
       <c r="F7" s="33">
-        <v>2.5159999999999998E-2</v>
+        <v>1.1941999999999999E-2</v>
       </c>
       <c r="G7" s="34" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
@@ -9953,7 +10117,7 @@
         <v>Normalized points allowed under HC</v>
       </c>
       <c r="F8" s="33">
-        <v>2.4913999999999999E-2</v>
+        <v>1.1936E-2</v>
       </c>
       <c r="G8" s="34" t="str">
         <v>Yes</v>
@@ -9964,16 +10128,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="31" t="str">
-        <v>QB_Avg_Games_Missed_Pct</v>
+        <v>QB_Min_Games_Missed_Pct</v>
       </c>
       <c r="D9" s="32">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E9" s="31" t="str">
-        <v>Average percentage of games missed by QBs</v>
+        <v>Minimum percentage of games missed by a QB</v>
       </c>
       <c r="F9" s="33">
-        <v>1.9039E-2</v>
+        <v>1.167E-2</v>
       </c>
       <c r="G9" s="34" t="str">
         <v/>
@@ -9984,19 +10148,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="31" t="str">
-        <v>PF (Points For)__hc_Norm</v>
+        <v>Active53-Man_Pct</v>
       </c>
       <c r="D10" s="32">
-        <v>302</v>
+        <v>5</v>
       </c>
       <c r="E10" s="31" t="str">
-        <v>Normalized points scored under HC</v>
+        <v>Active 53-man roster cap as percentage of maximum</v>
       </c>
       <c r="F10" s="33">
-        <v>1.8752999999999999E-2</v>
+        <v>1.1634E-2</v>
       </c>
       <c r="G10" s="34" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
@@ -10004,19 +10168,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="31" t="str">
-        <v>Avg_Roster_Experience</v>
+        <v>Yds__opp__hc_Norm</v>
       </c>
       <c r="D11" s="32">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="E11" s="31" t="str">
-        <v>Average experience of entire roster</v>
+        <v>Normalized yards allowed under HC</v>
       </c>
       <c r="F11" s="33">
-        <v>1.3277000000000001E-2</v>
+        <v>1.1449000000000001E-2</v>
       </c>
       <c r="G11" s="34" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
@@ -10024,19 +10188,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="31" t="str">
-        <v>Avg_Roster_Exp_OL</v>
+        <v>Sc%__opp__hc_Norm</v>
       </c>
       <c r="D12" s="32">
-        <v>176</v>
+        <v>356</v>
       </c>
       <c r="E12" s="31" t="str">
-        <v>Average experience of all offensive linemen</v>
+        <v>Normalized opponent scoring percentage under HC</v>
       </c>
       <c r="F12" s="33">
-        <v>1.2073E-2</v>
+        <v>1.0777E-2</v>
       </c>
       <c r="G12" s="34" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
@@ -10044,19 +10208,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="31" t="str">
-        <v>QB_Players_New</v>
+        <v>Pts Average Drive__opp__hc_Norm</v>
       </c>
       <c r="D13" s="32">
-        <v>24</v>
+        <v>361</v>
       </c>
       <c r="E13" s="31" t="str">
-        <v>Number of new QBs added to roster</v>
+        <v>Normalized opponent average points per drive under HC</v>
       </c>
       <c r="F13" s="33">
-        <v>1.1833E-2</v>
+        <v>1.065E-2</v>
       </c>
       <c r="G13" s="34" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
@@ -10064,19 +10228,19 @@
         <v>12</v>
       </c>
       <c r="C14" s="31" t="str">
-        <v>Sc%__hc_Norm</v>
+        <v>QB_Avg_Games_Missed_Pct</v>
       </c>
       <c r="D14" s="32">
-        <v>323</v>
+        <v>113</v>
       </c>
       <c r="E14" s="31" t="str">
-        <v>Normalized scoring percentage under HC</v>
+        <v>Average percentage of games missed by QBs</v>
       </c>
       <c r="F14" s="33">
-        <v>1.1734E-2</v>
+        <v>8.7139999999999995E-3</v>
       </c>
       <c r="G14" s="34" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.35">
@@ -10084,19 +10248,19 @@
         <v>13</v>
       </c>
       <c r="C15" s="31" t="str">
-        <v>Yds Average Drive__opp__hc_Norm</v>
+        <v>Avg_Starter_Experience</v>
       </c>
       <c r="D15" s="32">
-        <v>360</v>
+        <v>151</v>
       </c>
       <c r="E15" s="31" t="str">
-        <v>Normalized opponent average yards per drive under HC</v>
+        <v>Average experience of all starters</v>
       </c>
       <c r="F15" s="33">
-        <v>1.1140000000000001E-2</v>
+        <v>8.1969999999999994E-3</v>
       </c>
       <c r="G15" s="34" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
@@ -10104,19 +10268,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="31" t="str">
-        <v>Active53-Man_Pct</v>
+        <v>Y/P__opp__hc_Norm</v>
       </c>
       <c r="D16" s="32">
-        <v>5</v>
+        <v>337</v>
       </c>
       <c r="E16" s="31" t="str">
-        <v>Active 53-man roster cap as percentage of maximum</v>
+        <v>Normalized yards per play allowed under HC</v>
       </c>
       <c r="F16" s="33">
-        <v>1.0966999999999999E-2</v>
+        <v>7.626E-3</v>
       </c>
       <c r="G16" s="34" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
@@ -10124,16 +10288,16 @@
         <v>15</v>
       </c>
       <c r="C17" s="31" t="str">
-        <v>Avg_Starter_Experience</v>
+        <v>Avg_Roster_Exp_QB</v>
       </c>
       <c r="D17" s="32">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E17" s="31" t="str">
-        <v>Average experience of all starters</v>
+        <v>Average experience of all QBs on roster</v>
       </c>
       <c r="F17" s="33">
-        <v>1.0911000000000001E-2</v>
+        <v>7.4780000000000003E-3</v>
       </c>
       <c r="G17" s="34" t="str">
         <v/>
@@ -10144,19 +10308,19 @@
         <v>16</v>
       </c>
       <c r="C18" s="31" t="str">
-        <v>DL_Min_Games_Missed_Pct</v>
+        <v>NY/A Passing__opp__hc_Norm</v>
       </c>
       <c r="D18" s="32">
-        <v>135</v>
+        <v>345</v>
       </c>
       <c r="E18" s="31" t="str">
-        <v>Minimum percentage of games missed by D-line</v>
+        <v>Normalized net yards per pass allowed under HC</v>
       </c>
       <c r="F18" s="33">
-        <v>1.0317E-2</v>
+        <v>7.378E-3</v>
       </c>
       <c r="G18" s="34" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -10164,16 +10328,16 @@
         <v>17</v>
       </c>
       <c r="C19" s="31" t="str">
-        <v>Avg_Starter_Age</v>
+        <v>QB_Players_New</v>
       </c>
       <c r="D19" s="32">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="E19" s="31" t="str">
-        <v>Average age of all starters</v>
+        <v>Number of new QBs added to roster</v>
       </c>
       <c r="F19" s="33">
-        <v>1.0211E-2</v>
+        <v>6.515E-3</v>
       </c>
       <c r="G19" s="34" t="str">
         <v/>
@@ -10184,16 +10348,16 @@
         <v>18</v>
       </c>
       <c r="C20" s="31" t="str">
-        <v>RZAtt__hc_Norm</v>
+        <v>4DAtt__oc_Norm</v>
       </c>
       <c r="D20" s="32">
-        <v>333</v>
+        <v>265</v>
       </c>
       <c r="E20" s="31" t="str">
-        <v>Normalized red zone attempts under HC</v>
+        <v>Normalized fourth down attempts under OC</v>
       </c>
       <c r="F20" s="33">
-        <v>9.6399999999999993E-3</v>
+        <v>6.3369999999999998E-3</v>
       </c>
       <c r="G20" s="34" t="str">
         <v>Yes</v>
@@ -10204,19 +10368,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="31" t="str">
-        <v>Pts Average Drive__opp__hc_Norm</v>
+        <v>QB_New_Player_Rate_Pct</v>
       </c>
       <c r="D21" s="32">
-        <v>361</v>
+        <v>27</v>
       </c>
       <c r="E21" s="31" t="str">
-        <v>Normalized opponent average points per drive under HC</v>
+        <v>Percentage of new QBs on roster</v>
       </c>
       <c r="F21" s="33">
-        <v>9.5379999999999996E-3</v>
+        <v>6.3369999999999998E-3</v>
       </c>
       <c r="G21" s="34" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10224,19 +10388,19 @@
         <v>20</v>
       </c>
       <c r="C22" s="36" t="str">
-        <v>Y/P__opp__hc_Norm</v>
+        <v>QB_Departure_Rate_Pct</v>
       </c>
       <c r="D22" s="37">
-        <v>337</v>
+        <v>26</v>
       </c>
       <c r="E22" s="36" t="str">
-        <v>Normalized yards per play allowed under HC</v>
+        <v>Percentage of QBs departed from previous year</v>
       </c>
       <c r="F22" s="38">
-        <v>8.4460000000000004E-3</v>
+        <v>6.2579999999999997E-3</v>
       </c>
       <c r="G22" s="39" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.35">
@@ -10272,13 +10436,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>658</v>
+        <v>130</v>
       </c>
       <c r="D26" s="20">
-        <v>5.0374000000000002E-2</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>733</v>
+        <v>2.2554999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
@@ -10286,10 +10447,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D27" s="20">
-        <v>3.2133000000000002E-2</v>
+        <v>1.4893999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -10297,13 +10458,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>652</v>
+        <v>396</v>
       </c>
       <c r="D28" s="20">
-        <v>2.7653E-2</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>733</v>
+        <v>1.4399E-2</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
@@ -10311,10 +10469,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>390</v>
+        <v>267</v>
       </c>
       <c r="D29" s="20">
-        <v>2.7071000000000001E-2</v>
+        <v>1.2807000000000001E-2</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
@@ -10322,10 +10480,13 @@
         <v>5</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>130</v>
+        <v>584</v>
       </c>
       <c r="D30" s="20">
-        <v>2.5159999999999998E-2</v>
+        <v>1.1941999999999999E-2</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.35">
@@ -10336,7 +10497,7 @@
         <v>650</v>
       </c>
       <c r="D31" s="20">
-        <v>2.4913999999999999E-2</v>
+        <v>1.1936E-2</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>733</v>
@@ -10347,10 +10508,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D32" s="20">
-        <v>1.9039E-2</v>
+        <v>1.167E-2</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.35">
@@ -10358,13 +10519,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>584</v>
+        <v>128</v>
       </c>
       <c r="D33" s="20">
-        <v>1.8752999999999999E-2</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>733</v>
+        <v>1.1634E-2</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.35">
@@ -10372,10 +10530,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>314</v>
+        <v>652</v>
       </c>
       <c r="D34" s="20">
-        <v>1.3277000000000001E-2</v>
+        <v>1.1449000000000001E-2</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
@@ -10383,10 +10544,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>356</v>
+        <v>692</v>
       </c>
       <c r="D35" s="20">
-        <v>1.2073E-2</v>
+        <v>1.0777E-2</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
@@ -10394,10 +10558,13 @@
         <v>11</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>137</v>
+        <v>702</v>
       </c>
       <c r="D36" s="20">
-        <v>1.1833E-2</v>
+        <v>1.065E-2</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
@@ -10405,13 +10572,10 @@
         <v>12</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>626</v>
+        <v>266</v>
       </c>
       <c r="D37" s="20">
-        <v>1.1734E-2</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>733</v>
+        <v>8.7139999999999995E-3</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.35">
@@ -10419,13 +10583,10 @@
         <v>13</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>700</v>
+        <v>306</v>
       </c>
       <c r="D38" s="20">
-        <v>1.1140000000000001E-2</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>733</v>
+        <v>8.1969999999999994E-3</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.35">
@@ -10433,10 +10594,13 @@
         <v>14</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>128</v>
+        <v>654</v>
       </c>
       <c r="D39" s="20">
-        <v>1.0966999999999999E-2</v>
+        <v>7.626E-3</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.35">
@@ -10444,10 +10608,10 @@
         <v>15</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D40" s="20">
-        <v>1.0911000000000001E-2</v>
+        <v>7.4780000000000003E-3</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
@@ -10455,10 +10619,13 @@
         <v>16</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>288</v>
+        <v>670</v>
       </c>
       <c r="D41" s="20">
-        <v>1.0317E-2</v>
+        <v>7.378E-3</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.35">
@@ -10466,10 +10633,10 @@
         <v>17</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="D42" s="20">
-        <v>1.0211E-2</v>
+        <v>6.515E-3</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
@@ -10477,10 +10644,10 @@
         <v>18</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>646</v>
+        <v>510</v>
       </c>
       <c r="D43" s="20">
-        <v>9.6399999999999993E-3</v>
+        <v>6.3369999999999998E-3</v>
       </c>
       <c r="E43" s="20" t="s">
         <v>733</v>
@@ -10491,13 +10658,10 @@
         <v>19</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>702</v>
+        <v>141</v>
       </c>
       <c r="D44" s="20">
-        <v>9.5379999999999996E-3</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>733</v>
+        <v>6.3369999999999998E-3</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.35">
@@ -10505,13 +10669,10 @@
         <v>20</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>654</v>
+        <v>140</v>
       </c>
       <c r="D45" s="20">
-        <v>8.4460000000000004E-3</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>733</v>
+        <v>6.2579999999999997E-3</v>
       </c>
     </row>
   </sheetData>
@@ -10522,7 +10683,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCFCB0D-7AA5-46B7-B208-6DBB8BFFB381}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B1:P24"/>
+  <dimension ref="B1:P25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="20"/>
@@ -10609,44 +10770,44 @@
       </c>
       <c r="C3" s="27" t="str" cm="1">
         <f t="array" ref="C3:G12">J3:N12</f>
-        <v>CLT</v>
+        <v>CHI</v>
       </c>
       <c r="D3" s="27">
-        <v>2009</v>
+        <v>1987</v>
       </c>
       <c r="E3" s="42" t="str">
-        <v>Jim Caldwell</v>
+        <v>Mike Ditka</v>
       </c>
       <c r="F3" s="28">
-        <v>0.875</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="G3" s="28">
-        <v>0.45100000000000001</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="H3" s="48" cm="1">
         <f t="array" ref="H3:H12">(F3:F12-G3:G12)*16</f>
-        <v>6.7839999999999998</v>
+        <v>7.0720000000000001</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="K3" s="20">
-        <v>2009</v>
+        <v>1987</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="M3" s="20">
-        <v>0.875</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="N3" s="20">
-        <v>0.45100000000000001</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="O3" s="20">
-        <v>0.42399999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="P3" s="20">
-        <v>0.183</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.35">
@@ -10654,43 +10815,43 @@
         <v>2</v>
       </c>
       <c r="C4" s="32" t="str">
-        <v>CHI</v>
+        <v>CLT</v>
       </c>
       <c r="D4" s="32">
-        <v>1987</v>
+        <v>2009</v>
       </c>
       <c r="E4" s="43" t="str">
-        <v>Mike Ditka</v>
+        <v>Jim Caldwell</v>
       </c>
       <c r="F4" s="33">
-        <v>0.73299999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="G4" s="33">
-        <v>0.32</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="H4" s="49">
-        <v>6.6079999999999997</v>
+        <v>6.5439999999999996</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="K4" s="20">
-        <v>1987</v>
+        <v>2009</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="M4" s="20">
-        <v>0.73299999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="N4" s="20">
-        <v>0.32</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="O4" s="20">
-        <v>0.41299999999999998</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="P4" s="20">
-        <v>0.158</v>
+        <v>9.7000000000000003E-2</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
@@ -10710,10 +10871,10 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="G5" s="33">
-        <v>0.51600000000000001</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="H5" s="49">
-        <v>5.968</v>
+        <v>5.92</v>
       </c>
       <c r="J5" s="20" t="s">
         <v>783</v>
@@ -10728,13 +10889,13 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="N5" s="20">
-        <v>0.51600000000000001</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="O5" s="20">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="P5" s="20">
-        <v>0.13200000000000001</v>
+        <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
@@ -10742,43 +10903,43 @@
         <v>4</v>
       </c>
       <c r="C6" s="32" t="str">
-        <v>NWE</v>
+        <v>RAI</v>
       </c>
       <c r="D6" s="32">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="E6" s="43" t="str">
-        <v>Bill Belichick</v>
+        <v>John Madden</v>
       </c>
       <c r="F6" s="33">
-        <v>1</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="G6" s="33">
-        <v>0.66100000000000003</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="H6" s="49">
-        <v>5.4239999999999995</v>
+        <v>4.9920000000000009</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>819</v>
+        <v>787</v>
       </c>
       <c r="K6" s="20">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
       <c r="M6" s="20">
-        <v>1</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="N6" s="20">
-        <v>0.66100000000000003</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="O6" s="20">
-        <v>0.33900000000000002</v>
+        <v>0.312</v>
       </c>
       <c r="P6" s="20">
-        <v>8.6999999999999994E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
@@ -10786,43 +10947,43 @@
         <v>5</v>
       </c>
       <c r="C7" s="32" t="str">
-        <v>CLT</v>
+        <v>DET</v>
       </c>
       <c r="D7" s="32">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="43" t="str">
-        <v>Jim Mora Sr</v>
+        <v>Dan Campbell</v>
       </c>
       <c r="F7" s="33">
-        <v>0.81200000000000006</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="G7" s="33">
-        <v>0.5</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="H7" s="49">
-        <v>4.9920000000000009</v>
+        <v>4.9760000000000009</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>779</v>
+        <v>808</v>
       </c>
       <c r="K7" s="20">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="M7" s="20">
-        <v>0.81200000000000006</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="N7" s="20">
-        <v>0.5</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="O7" s="20">
         <v>0.312</v>
       </c>
       <c r="P7" s="20">
-        <v>0.21199999999999999</v>
+        <v>7.2999999999999995E-2</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
@@ -10830,43 +10991,43 @@
         <v>6</v>
       </c>
       <c r="C8" s="32" t="str">
-        <v>NOR</v>
+        <v>SFO</v>
       </c>
       <c r="D8" s="32">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="E8" s="43" t="str">
-        <v>Sean Payton</v>
+        <v>Bill Walsh</v>
       </c>
       <c r="F8" s="33">
-        <v>0.81200000000000006</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="G8" s="33">
-        <v>0.51400000000000001</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="H8" s="49">
-        <v>4.7680000000000007</v>
+        <v>4.9439999999999991</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="K8" s="20">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="M8" s="20">
-        <v>0.81200000000000006</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="N8" s="20">
-        <v>0.51400000000000001</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="O8" s="20">
-        <v>0.29799999999999999</v>
+        <v>0.309</v>
       </c>
       <c r="P8" s="20">
-        <v>8.7999999999999995E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.35">
@@ -10874,43 +11035,43 @@
         <v>7</v>
       </c>
       <c r="C9" s="32" t="str">
-        <v>DET</v>
+        <v>NYG</v>
       </c>
       <c r="D9" s="32">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="E9" s="43" t="str">
-        <v>Dan Campbell</v>
+        <v>Bill Parcells</v>
       </c>
       <c r="F9" s="33">
-        <v>0.88200000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G9" s="33">
-        <v>0.58699999999999997</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="H9" s="49">
-        <v>4.7200000000000006</v>
+        <v>4.8960000000000008</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>809</v>
+        <v>930</v>
       </c>
       <c r="K9" s="20">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>815</v>
+        <v>931</v>
       </c>
       <c r="M9" s="20">
-        <v>0.88200000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="N9" s="20">
-        <v>0.58699999999999997</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="O9" s="20">
-        <v>0.29499999999999998</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="P9" s="20">
-        <v>0.114</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -10930,10 +11091,10 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="G10" s="33">
-        <v>0.59399999999999997</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="H10" s="49">
-        <v>4.7200000000000006</v>
+        <v>4.8160000000000007</v>
       </c>
       <c r="J10" s="20" t="s">
         <v>787</v>
@@ -10948,13 +11109,13 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="N10" s="20">
-        <v>0.59399999999999997</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="O10" s="20">
-        <v>0.29499999999999998</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="P10" s="20">
-        <v>0.108</v>
+        <v>8.7999999999999995E-2</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.35">
@@ -10962,43 +11123,43 @@
         <v>9</v>
       </c>
       <c r="C11" s="32" t="str">
-        <v>MIA</v>
+        <v>NOR</v>
       </c>
       <c r="D11" s="32">
-        <v>1974</v>
+        <v>2011</v>
       </c>
       <c r="E11" s="43" t="str">
-        <v>Don Shula</v>
+        <v>Sean Payton</v>
       </c>
       <c r="F11" s="33">
-        <v>0.78600000000000003</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="G11" s="33">
-        <v>0.49199999999999999</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H11" s="49">
-        <v>4.7040000000000006</v>
+        <v>4.7520000000000007</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>821</v>
+        <v>785</v>
       </c>
       <c r="K11" s="20">
-        <v>1974</v>
+        <v>2011</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="M11" s="20">
-        <v>0.78600000000000003</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="N11" s="20">
-        <v>0.49199999999999999</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="O11" s="20">
-        <v>0.29399999999999998</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="P11" s="20">
-        <v>7.6999999999999999E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11006,552 +11167,561 @@
         <v>10</v>
       </c>
       <c r="C12" s="37" t="str">
-        <v>SFO</v>
+        <v>PIT</v>
       </c>
       <c r="D12" s="37">
-        <v>1987</v>
+        <v>2004</v>
       </c>
       <c r="E12" s="44" t="str">
-        <v>Bill Walsh</v>
+        <v>Bill Cowher</v>
       </c>
       <c r="F12" s="38">
-        <v>0.86699999999999999</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="G12" s="38">
-        <v>0.57299999999999995</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="H12" s="50">
-        <v>4.7040000000000006</v>
+        <v>4.7519999999999989</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>822</v>
+        <v>932</v>
       </c>
       <c r="K12" s="20">
-        <v>1987</v>
+        <v>2004</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>823</v>
+        <v>933</v>
       </c>
       <c r="M12" s="20">
-        <v>0.86699999999999999</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="N12" s="20">
-        <v>0.57299999999999995</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="O12" s="20">
-        <v>0.29399999999999998</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="P12" s="20">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J13" s="20" t="s">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="118"/>
+    </row>
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J14" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K14" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L14" s="20" t="s">
         <v>767</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M14" s="20" t="s">
         <v>768</v>
       </c>
-      <c r="N13" s="20" t="s">
+      <c r="N14" s="20" t="s">
         <v>769</v>
       </c>
-      <c r="O13" s="20" t="s">
+      <c r="O14" s="20" t="s">
         <v>770</v>
       </c>
-      <c r="P13" s="20" t="s">
+      <c r="P14" s="20" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="51" t="s">
+    <row r="15" spans="2:16" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="51" t="s">
         <v>763</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C15" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D15" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E15" s="53" t="s">
         <v>767</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F15" s="52" t="s">
         <v>789</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="G15" s="52" t="s">
         <v>790</v>
       </c>
-      <c r="H14" s="54" t="s">
+      <c r="H15" s="54" t="s">
         <v>770</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J15" s="20" t="s">
         <v>772</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="K15" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="L14" s="20" t="s">
+      <c r="L15" s="20" t="s">
         <v>774</v>
       </c>
-      <c r="M14" s="20" t="s">
+      <c r="M15" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="N14" s="20" t="s">
+      <c r="N15" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="O14" s="20" t="s">
+      <c r="O15" s="20" t="s">
         <v>777</v>
       </c>
-      <c r="P14" s="20" t="s">
+      <c r="P15" s="20" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="25">
+    <row r="16" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="25">
         <v>1</v>
       </c>
-      <c r="C15" s="27" t="str" cm="1">
-        <f t="array" ref="C15:G24">J15:N24</f>
-        <v>SEA</v>
-      </c>
-      <c r="D15" s="27">
-        <v>1976</v>
-      </c>
-      <c r="E15" s="42" t="str">
-        <v>Jack Patera</v>
-      </c>
-      <c r="F15" s="28">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="G15" s="28">
-        <v>0.47</v>
-      </c>
-      <c r="H15" s="48" cm="1">
-        <f t="array" ref="H15:H24">(F15:F24-G15:G24)*16</f>
-        <v>-5.2319999999999993</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>824</v>
-      </c>
-      <c r="K15" s="20">
-        <v>1976</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>825</v>
-      </c>
-      <c r="M15" s="20">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="N15" s="20">
-        <v>0.47</v>
-      </c>
-      <c r="O15" s="20">
-        <v>-0.32700000000000001</v>
-      </c>
-      <c r="P15" s="20">
-        <v>-0.108</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B16" s="30">
-        <v>2</v>
-      </c>
-      <c r="C16" s="32" t="str">
-        <v>NOR</v>
-      </c>
-      <c r="D16" s="32">
-        <v>1996</v>
-      </c>
-      <c r="E16" s="43" t="str">
-        <v>Jim Mora Sr</v>
-      </c>
-      <c r="F16" s="33">
-        <v>0.188</v>
-      </c>
-      <c r="G16" s="33">
-        <v>0.501</v>
-      </c>
-      <c r="H16" s="49">
-        <v>-5.008</v>
+      <c r="C16" s="27" t="str" cm="1">
+        <f t="array" ref="C16:G25">J16:N25</f>
+        <v>ATL</v>
+      </c>
+      <c r="D16" s="27">
+        <v>2020</v>
+      </c>
+      <c r="E16" s="42" t="str">
+        <v>Dan Quinn</v>
+      </c>
+      <c r="F16" s="28">
+        <v>0</v>
+      </c>
+      <c r="G16" s="28">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="H16" s="48" cm="1">
+        <f t="array" ref="H16:H25">(F16:F25-G16:G25)*16</f>
+        <v>-8.3680000000000003</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>785</v>
+        <v>819</v>
       </c>
       <c r="K16" s="20">
-        <v>1996</v>
+        <v>2020</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="M16" s="20">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="N16" s="20">
-        <v>0.501</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="O16" s="20">
-        <v>-0.314</v>
+        <v>-0.52300000000000002</v>
       </c>
       <c r="P16" s="20">
-        <v>-0.151</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B17" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="32" t="str">
-        <v>SEA</v>
+        <v>PHI</v>
       </c>
       <c r="D17" s="32">
-        <v>1992</v>
+        <v>1971</v>
       </c>
       <c r="E17" s="43" t="str">
-        <v>Tom Flores</v>
+        <v>Jerry Williams</v>
       </c>
       <c r="F17" s="33">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="G17" s="33">
-        <v>0.436</v>
+        <v>0.442</v>
       </c>
       <c r="H17" s="49">
-        <v>-4.976</v>
+        <v>-7.0720000000000001</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>824</v>
+        <v>934</v>
       </c>
       <c r="K17" s="20">
-        <v>1992</v>
+        <v>1971</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>788</v>
+        <v>935</v>
       </c>
       <c r="M17" s="20">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="N17" s="20">
-        <v>0.436</v>
+        <v>0.442</v>
       </c>
       <c r="O17" s="20">
-        <v>-0.311</v>
+        <v>-0.442</v>
       </c>
       <c r="P17" s="20">
-        <v>-0.06</v>
+        <v>-4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B18" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="32" t="str">
-        <v>CHI</v>
+        <v>CIN</v>
       </c>
       <c r="D18" s="32">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="E18" s="43" t="str">
-        <v>Matt Eberflus</v>
+        <v>David Shula</v>
       </c>
       <c r="F18" s="33">
-        <v>0.29399999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="G18" s="33">
-        <v>0.6</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="H18" s="49">
-        <v>-4.8959999999999999</v>
+        <v>-6.911999999999999</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>781</v>
+        <v>936</v>
       </c>
       <c r="K18" s="20">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>813</v>
+        <v>937</v>
       </c>
       <c r="M18" s="20">
-        <v>0.29399999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="N18" s="20">
-        <v>0.6</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="O18" s="20">
-        <v>-0.30599999999999999</v>
+        <v>-0.432</v>
       </c>
       <c r="P18" s="20">
-        <v>-0.153</v>
+        <v>-0.14799999999999999</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B19" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="32" t="str">
-        <v>CLT</v>
+        <v>HTX</v>
       </c>
       <c r="D19" s="32">
-        <v>1991</v>
+        <v>2020</v>
       </c>
       <c r="E19" s="43" t="str">
-        <v>Ron Meyer</v>
+        <v>Bill O'Brien</v>
       </c>
       <c r="F19" s="33">
-        <v>6.2E-2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="33">
-        <v>0.36399999999999999</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="H19" s="49">
-        <v>-4.8319999999999999</v>
+        <v>-6.64</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>779</v>
+        <v>938</v>
       </c>
       <c r="K19" s="20">
-        <v>1991</v>
+        <v>2020</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>811</v>
+        <v>939</v>
       </c>
       <c r="M19" s="20">
-        <v>6.2E-2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="20">
-        <v>0.36399999999999999</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="O19" s="20">
-        <v>-0.30199999999999999</v>
+        <v>-0.41499999999999998</v>
       </c>
       <c r="P19" s="20">
-        <v>-0.14899999999999999</v>
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="32" t="str">
-        <v>CAR</v>
+        <v>SEA</v>
       </c>
       <c r="D20" s="32">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="E20" s="43" t="str">
-        <v>George Seifert</v>
+        <v>Jack Patera</v>
       </c>
       <c r="F20" s="33">
-        <v>6.2E-2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="33">
-        <v>0.35599999999999998</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="H20" s="49">
-        <v>-4.7039999999999997</v>
+        <v>-6.3680000000000003</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K20" s="20">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M20" s="20">
-        <v>6.2E-2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="20">
-        <v>0.35599999999999998</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="O20" s="20">
-        <v>-0.29299999999999998</v>
+        <v>-0.39800000000000002</v>
       </c>
       <c r="P20" s="20">
-        <v>-9.1999999999999998E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B21" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="32" t="str">
-        <v>DET</v>
+        <v>CLT</v>
       </c>
       <c r="D21" s="32">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="E21" s="43" t="str">
-        <v>Marty Mornhinweg</v>
+        <v>Ron Meyer</v>
       </c>
       <c r="F21" s="33">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="G21" s="33">
-        <v>0.41499999999999998</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="H21" s="49">
-        <v>-4.6399999999999997</v>
+        <v>-5.7119999999999997</v>
       </c>
       <c r="J21" s="20" t="s">
+        <v>779</v>
+      </c>
+      <c r="K21" s="20">
+        <v>1991</v>
+      </c>
+      <c r="L21" s="20" t="s">
         <v>809</v>
       </c>
-      <c r="K21" s="20">
-        <v>2001</v>
-      </c>
-      <c r="L21" s="20" t="s">
-        <v>810</v>
-      </c>
       <c r="M21" s="20">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="N21" s="20">
-        <v>0.41499999999999998</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="O21" s="20">
-        <v>-0.28999999999999998</v>
+        <v>-0.35699999999999998</v>
       </c>
       <c r="P21" s="20">
-        <v>-0.156</v>
+        <v>-4.7E-2</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="32" t="str">
-        <v>ATL</v>
+        <v>CLT</v>
       </c>
       <c r="D22" s="32">
-        <v>2020</v>
+        <v>1972</v>
       </c>
       <c r="E22" s="43" t="str">
-        <v>Dan Quinn</v>
+        <v>Don McCafferty</v>
       </c>
       <c r="F22" s="33">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G22" s="33">
-        <v>0.53500000000000003</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="H22" s="49">
-        <v>-4.5600000000000005</v>
+        <v>-5.4720000000000004</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>826</v>
+        <v>779</v>
       </c>
       <c r="K22" s="20">
-        <v>2020</v>
+        <v>1972</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>827</v>
+        <v>940</v>
       </c>
       <c r="M22" s="20">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N22" s="20">
-        <v>0.53500000000000003</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="O22" s="20">
-        <v>-0.28499999999999998</v>
+        <v>-0.34200000000000003</v>
       </c>
       <c r="P22" s="20">
-        <v>-7.4999999999999997E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B23" s="30">
+        <v>8</v>
+      </c>
+      <c r="C23" s="32" t="str">
+        <v>SFO</v>
+      </c>
+      <c r="D23" s="32">
+        <v>1979</v>
+      </c>
+      <c r="E23" s="43" t="str">
+        <v>Bill Walsh</v>
+      </c>
+      <c r="F23" s="33">
+        <v>0.125</v>
+      </c>
+      <c r="G23" s="33">
+        <v>0.442</v>
+      </c>
+      <c r="H23" s="49">
+        <v>-5.0720000000000001</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>815</v>
+      </c>
+      <c r="K23" s="20">
+        <v>1979</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>816</v>
+      </c>
+      <c r="M23" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="N23" s="20">
+        <v>0.442</v>
+      </c>
+      <c r="O23" s="20">
+        <v>-0.317</v>
+      </c>
+      <c r="P23" s="20">
+        <v>-3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B24" s="30">
         <v>9</v>
       </c>
-      <c r="C23" s="32" t="str">
-        <v>RAI</v>
-      </c>
-      <c r="D23" s="32">
-        <v>1997</v>
-      </c>
-      <c r="E23" s="43" t="str">
-        <v>Joe Bugel</v>
-      </c>
-      <c r="F23" s="33">
+      <c r="C24" s="32" t="str">
+        <v>DET</v>
+      </c>
+      <c r="D24" s="32">
+        <v>1976</v>
+      </c>
+      <c r="E24" s="43" t="str">
+        <v>Rick Forzano</v>
+      </c>
+      <c r="F24" s="33">
         <v>0.25</v>
       </c>
-      <c r="G23" s="33">
-        <v>0.52700000000000002</v>
-      </c>
-      <c r="H23" s="49">
-        <v>-4.4320000000000004</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>787</v>
-      </c>
-      <c r="K23" s="20">
-        <v>1997</v>
-      </c>
-      <c r="L23" s="20" t="s">
-        <v>828</v>
-      </c>
-      <c r="M23" s="20">
+      <c r="G24" s="33">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="H24" s="49">
+        <v>-5.0239999999999991</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>808</v>
+      </c>
+      <c r="K24" s="20">
+        <v>1976</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>941</v>
+      </c>
+      <c r="M24" s="20">
         <v>0.25</v>
       </c>
-      <c r="N23" s="20">
-        <v>0.52700000000000002</v>
-      </c>
-      <c r="O23" s="20">
-        <v>-0.27700000000000002</v>
-      </c>
-      <c r="P23" s="20">
-        <v>-0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="35">
+      <c r="N24" s="20">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="O24" s="20">
+        <v>-0.314</v>
+      </c>
+      <c r="P24" s="20">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="35">
         <v>10</v>
       </c>
-      <c r="C24" s="37" t="str">
-        <v>WAS</v>
-      </c>
-      <c r="D24" s="37">
-        <v>1994</v>
-      </c>
-      <c r="E24" s="44" t="str">
-        <v>Norv Turner</v>
-      </c>
-      <c r="F24" s="38">
-        <v>0.188</v>
-      </c>
-      <c r="G24" s="38">
-        <v>0.46</v>
-      </c>
-      <c r="H24" s="50">
-        <v>-4.3520000000000003</v>
-      </c>
-      <c r="J24" s="20" t="s">
-        <v>783</v>
-      </c>
-      <c r="K24" s="20">
-        <v>1994</v>
-      </c>
-      <c r="L24" s="20" t="s">
-        <v>829</v>
-      </c>
-      <c r="M24" s="20">
-        <v>0.188</v>
-      </c>
-      <c r="N24" s="20">
-        <v>0.46</v>
-      </c>
-      <c r="O24" s="20">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="P24" s="20">
-        <v>-4.7E-2</v>
+      <c r="C25" s="37" t="str">
+        <v>CIN</v>
+      </c>
+      <c r="D25" s="37">
+        <v>1971</v>
+      </c>
+      <c r="E25" s="44" t="str">
+        <v>Paul Brown</v>
+      </c>
+      <c r="F25" s="38">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="G25" s="38">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="H25" s="50">
+        <v>-4.944</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K25" s="20">
+        <v>1971</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>942</v>
+      </c>
+      <c r="M25" s="20">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="N25" s="20">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="O25" s="20">
+        <v>-0.31</v>
+      </c>
+      <c r="P25" s="20">
+        <v>-0.109</v>
       </c>
     </row>
   </sheetData>
@@ -11567,7 +11737,7 @@
   <cols>
     <col min="1" max="1" width="8.7265625" style="20"/>
     <col min="2" max="2" width="6.81640625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="57" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" style="56" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.453125" style="40" customWidth="1"/>
     <col min="5" max="5" width="13.81640625" style="20" customWidth="1"/>
     <col min="6" max="6" width="16.54296875" style="40" customWidth="1"/>
@@ -11599,13 +11769,28 @@
         <v>767</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>793</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>805</v>
+      </c>
+      <c r="H2" s="55" t="s">
+        <v>943</v>
+      </c>
+      <c r="I2" s="55" t="s">
+        <v>775</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>944</v>
+      </c>
+      <c r="K2" s="55" t="s">
+        <v>776</v>
+      </c>
+      <c r="L2" s="55" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
@@ -11620,25 +11805,25 @@
         <f t="array" ref="D3:D17">J3:J17</f>
         <v>3</v>
       </c>
-      <c r="E3" s="58" cm="1">
+      <c r="E3" s="57" cm="1">
         <f t="array" ref="E3:E17">K3:K17*16</f>
-        <v>7.0895999999999999</v>
+        <v>7.7728000000000002</v>
       </c>
       <c r="F3" s="48" cm="1">
         <f t="array" ref="F3:F17">I3:I17*16</f>
-        <v>2.3632</v>
+        <v>2.5903999999999998</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>796</v>
       </c>
       <c r="I3" s="20">
-        <v>0.1477</v>
+        <v>0.16189999999999999</v>
       </c>
       <c r="J3" s="20">
         <v>3</v>
       </c>
       <c r="K3" s="20">
-        <v>0.44309999999999999</v>
+        <v>0.48580000000000001</v>
       </c>
       <c r="L3" s="20">
         <v>0.66700000000000004</v>
@@ -11649,31 +11834,31 @@
         <v>2</v>
       </c>
       <c r="C4" s="43" t="str">
-        <v>Mike Martz</v>
+        <v>Don Shula</v>
       </c>
       <c r="D4" s="32">
-        <v>6</v>
-      </c>
-      <c r="E4" s="59">
-        <v>12.9856</v>
+        <v>26</v>
+      </c>
+      <c r="E4" s="58">
+        <v>57.854399999999998</v>
       </c>
       <c r="F4" s="49">
-        <v>2.1648000000000001</v>
+        <v>2.2256</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>830</v>
+        <v>801</v>
       </c>
       <c r="I4" s="20">
-        <v>0.1353</v>
+        <v>0.1391</v>
       </c>
       <c r="J4" s="20">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K4" s="20">
-        <v>0.81159999999999999</v>
+        <v>3.6158999999999999</v>
       </c>
       <c r="L4" s="20">
-        <v>0.59399999999999997</v>
+        <v>0.66300000000000003</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -11681,31 +11866,31 @@
         <v>3</v>
       </c>
       <c r="C5" s="43" t="str">
-        <v>Mike McDaniel</v>
+        <v>John Madden</v>
       </c>
       <c r="D5" s="32">
-        <v>3</v>
-      </c>
-      <c r="E5" s="59">
-        <v>6.0608000000000004</v>
+        <v>9</v>
+      </c>
+      <c r="E5" s="58">
+        <v>17.0944</v>
       </c>
       <c r="F5" s="49">
-        <v>2.0207999999999999</v>
+        <v>1.8992</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I5" s="20">
-        <v>0.1263</v>
+        <v>0.1187</v>
       </c>
       <c r="J5" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K5" s="20">
-        <v>0.37880000000000003</v>
+        <v>1.0684</v>
       </c>
       <c r="L5" s="20">
-        <v>0.54900000000000004</v>
+        <v>0.73699999999999999</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
@@ -11713,31 +11898,31 @@
         <v>4</v>
       </c>
       <c r="C6" s="43" t="str">
-        <v>Don Shula</v>
+        <v>Mike McDaniel</v>
       </c>
       <c r="D6" s="32">
-        <v>27</v>
-      </c>
-      <c r="E6" s="59">
-        <v>52.241599999999998</v>
+        <v>3</v>
+      </c>
+      <c r="E6" s="58">
+        <v>5.6448</v>
       </c>
       <c r="F6" s="49">
-        <v>1.9343999999999999</v>
+        <v>1.8815999999999999</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="I6" s="20">
-        <v>0.12089999999999999</v>
+        <v>0.1176</v>
       </c>
       <c r="J6" s="20">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K6" s="20">
-        <v>3.2650999999999999</v>
+        <v>0.3528</v>
       </c>
       <c r="L6" s="20">
-        <v>0.65400000000000003</v>
+        <v>0.54900000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -11745,31 +11930,31 @@
         <v>5</v>
       </c>
       <c r="C7" s="43" t="str">
-        <v>Tom Landry</v>
+        <v>Mike Martz</v>
       </c>
       <c r="D7" s="32">
-        <v>19</v>
-      </c>
-      <c r="E7" s="59">
-        <v>32.468800000000002</v>
+        <v>6</v>
+      </c>
+      <c r="E7" s="58">
+        <v>11.1248</v>
       </c>
       <c r="F7" s="49">
-        <v>1.7088000000000001</v>
+        <v>1.8544</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="I7" s="20">
-        <v>0.10680000000000001</v>
+        <v>0.1159</v>
       </c>
       <c r="J7" s="20">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K7" s="20">
-        <v>2.0293000000000001</v>
+        <v>0.69530000000000003</v>
       </c>
       <c r="L7" s="20">
-        <v>0.65700000000000003</v>
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -11777,31 +11962,31 @@
         <v>6</v>
       </c>
       <c r="C8" s="43" t="str">
-        <v>John Madden</v>
+        <v>John Ralston</v>
       </c>
       <c r="D8" s="32">
-        <v>9</v>
-      </c>
-      <c r="E8" s="59">
-        <v>15.2928</v>
+        <v>5</v>
+      </c>
+      <c r="E8" s="58">
+        <v>8.8192000000000004</v>
       </c>
       <c r="F8" s="49">
-        <v>1.6992</v>
+        <v>1.7632000000000001</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>799</v>
+        <v>823</v>
       </c>
       <c r="I8" s="20">
-        <v>0.1062</v>
+        <v>0.11020000000000001</v>
       </c>
       <c r="J8" s="20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K8" s="20">
-        <v>0.95579999999999998</v>
+        <v>0.55120000000000002</v>
       </c>
       <c r="L8" s="20">
-        <v>0.73699999999999999</v>
+        <v>0.50700000000000001</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
@@ -11809,31 +11994,31 @@
         <v>7</v>
       </c>
       <c r="C9" s="43" t="str">
-        <v>Chuck Pagano</v>
+        <v>Raymond Berry</v>
       </c>
       <c r="D9" s="32">
-        <v>6</v>
-      </c>
-      <c r="E9" s="59">
-        <v>10.137600000000001</v>
+        <v>5</v>
+      </c>
+      <c r="E9" s="58">
+        <v>8.6031999999999993</v>
       </c>
       <c r="F9" s="49">
-        <v>1.6896</v>
+        <v>1.72</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="I9" s="20">
-        <v>0.1056</v>
+        <v>0.1075</v>
       </c>
       <c r="J9" s="20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="20">
-        <v>0.63360000000000005</v>
+        <v>0.53769999999999996</v>
       </c>
       <c r="L9" s="20">
-        <v>0.55200000000000005</v>
+        <v>0.55700000000000005</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
@@ -11841,31 +12026,31 @@
         <v>8</v>
       </c>
       <c r="C10" s="43" t="str">
-        <v>Bruce Arians</v>
+        <v>Kevin Stefanski</v>
       </c>
       <c r="D10" s="32">
-        <v>8</v>
-      </c>
-      <c r="E10" s="59">
-        <v>13.252800000000001</v>
+        <v>5</v>
+      </c>
+      <c r="E10" s="58">
+        <v>8.0896000000000008</v>
       </c>
       <c r="F10" s="49">
-        <v>1.6559999999999999</v>
+        <v>1.6175999999999999</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="I10" s="20">
-        <v>0.10349999999999999</v>
+        <v>0.1011</v>
       </c>
       <c r="J10" s="20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K10" s="20">
-        <v>0.82830000000000004</v>
+        <v>0.50560000000000005</v>
       </c>
       <c r="L10" s="20">
-        <v>0.623</v>
+        <v>0.47899999999999998</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
@@ -11873,31 +12058,31 @@
         <v>9</v>
       </c>
       <c r="C11" s="43" t="str">
-        <v>Raymond Berry</v>
+        <v>Tom Landry</v>
       </c>
       <c r="D11" s="32">
-        <v>5</v>
-      </c>
-      <c r="E11" s="59">
-        <v>8.1760000000000002</v>
+        <v>19</v>
+      </c>
+      <c r="E11" s="58">
+        <v>28.963200000000001</v>
       </c>
       <c r="F11" s="49">
-        <v>1.6352</v>
+        <v>1.5247999999999999</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I11" s="20">
-        <v>0.1022</v>
+        <v>9.5299999999999996E-2</v>
       </c>
       <c r="J11" s="20">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K11" s="20">
-        <v>0.51100000000000001</v>
+        <v>1.8102</v>
       </c>
       <c r="L11" s="20">
-        <v>0.55700000000000005</v>
+        <v>0.65700000000000003</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
@@ -11905,31 +12090,31 @@
         <v>10</v>
       </c>
       <c r="C12" s="43" t="str">
-        <v>Kevin Stefanski</v>
+        <v>Bill Belichick</v>
       </c>
       <c r="D12" s="32">
-        <v>5</v>
-      </c>
-      <c r="E12" s="59">
-        <v>7.6159999999999997</v>
+        <v>29</v>
+      </c>
+      <c r="E12" s="58">
+        <v>43.7376</v>
       </c>
       <c r="F12" s="49">
-        <v>1.5232000000000001</v>
+        <v>1.5087999999999999</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="I12" s="20">
-        <v>9.5200000000000007E-2</v>
+        <v>9.4299999999999995E-2</v>
       </c>
       <c r="J12" s="20">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K12" s="20">
-        <v>0.47599999999999998</v>
+        <v>2.7336</v>
       </c>
       <c r="L12" s="20">
-        <v>0.47899999999999998</v>
+        <v>0.64800000000000002</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
@@ -11937,31 +12122,31 @@
         <v>11</v>
       </c>
       <c r="C13" s="43" t="str">
-        <v>Kyle Shanahan</v>
+        <v>Chuck Pagano</v>
       </c>
       <c r="D13" s="32">
-        <v>8</v>
-      </c>
-      <c r="E13" s="59">
-        <v>11.984</v>
+        <v>6</v>
+      </c>
+      <c r="E13" s="58">
+        <v>9.0191999999999997</v>
       </c>
       <c r="F13" s="49">
-        <v>1.4976</v>
+        <v>1.504</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>831</v>
+        <v>800</v>
       </c>
       <c r="I13" s="20">
-        <v>9.3600000000000003E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J13" s="20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K13" s="20">
-        <v>0.749</v>
+        <v>0.56369999999999998</v>
       </c>
       <c r="L13" s="20">
-        <v>0.52800000000000002</v>
+        <v>0.55200000000000005</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
@@ -11969,31 +12154,31 @@
         <v>12</v>
       </c>
       <c r="C14" s="43" t="str">
-        <v>John Ralston</v>
+        <v>Kyle Shanahan</v>
       </c>
       <c r="D14" s="32">
-        <v>5</v>
-      </c>
-      <c r="E14" s="59">
-        <v>7.008</v>
+        <v>8</v>
+      </c>
+      <c r="E14" s="58">
+        <v>12.016</v>
       </c>
       <c r="F14" s="49">
-        <v>1.4016</v>
+        <v>1.5024</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="I14" s="20">
-        <v>8.7599999999999997E-2</v>
+        <v>9.3899999999999997E-2</v>
       </c>
       <c r="J14" s="20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K14" s="20">
-        <v>0.438</v>
+        <v>0.751</v>
       </c>
       <c r="L14" s="20">
-        <v>0.50700000000000001</v>
+        <v>0.52800000000000002</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
@@ -12001,31 +12186,31 @@
         <v>13</v>
       </c>
       <c r="C15" s="43" t="str">
-        <v>Red Miller</v>
+        <v>Bruce Arians</v>
       </c>
       <c r="D15" s="32">
-        <v>4</v>
-      </c>
-      <c r="E15" s="59">
-        <v>5.5936000000000003</v>
+        <v>8</v>
+      </c>
+      <c r="E15" s="58">
+        <v>11.76</v>
       </c>
       <c r="F15" s="49">
-        <v>1.3984000000000001</v>
+        <v>1.4703999999999999</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>833</v>
+        <v>797</v>
       </c>
       <c r="I15" s="20">
-        <v>8.7400000000000005E-2</v>
+        <v>9.1899999999999996E-2</v>
       </c>
       <c r="J15" s="20">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" s="20">
-        <v>0.34960000000000002</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="L15" s="20">
-        <v>0.65200000000000002</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
@@ -12033,31 +12218,31 @@
         <v>14</v>
       </c>
       <c r="C16" s="43" t="str">
-        <v>Joe Gibbs</v>
+        <v>Red Miller</v>
       </c>
       <c r="D16" s="32">
-        <v>16</v>
-      </c>
-      <c r="E16" s="59">
-        <v>22.295999999999999</v>
+        <v>4</v>
+      </c>
+      <c r="E16" s="58">
+        <v>5.8592000000000004</v>
       </c>
       <c r="F16" s="49">
-        <v>1.3935999999999999</v>
+        <v>1.4656</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>784</v>
+        <v>824</v>
       </c>
       <c r="I16" s="20">
-        <v>8.7099999999999997E-2</v>
+        <v>9.1600000000000001E-2</v>
       </c>
       <c r="J16" s="20">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K16" s="20">
-        <v>1.3935</v>
+        <v>0.36620000000000003</v>
       </c>
       <c r="L16" s="20">
-        <v>0.629</v>
+        <v>0.65200000000000002</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12065,34 +12250,50 @@
         <v>15</v>
       </c>
       <c r="C17" s="44" t="str">
-        <v>Jim Caldwell</v>
+        <v>Mike Vrabel</v>
       </c>
       <c r="D17" s="37">
-        <v>7</v>
-      </c>
-      <c r="E17" s="60">
-        <v>9.6256000000000004</v>
+        <v>6</v>
+      </c>
+      <c r="E17" s="59">
+        <v>8.4128000000000007</v>
       </c>
       <c r="F17" s="50">
-        <v>1.3744000000000001</v>
+        <v>1.4016</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>780</v>
+        <v>945</v>
       </c>
       <c r="I17" s="20">
-        <v>8.5900000000000004E-2</v>
+        <v>8.7599999999999997E-2</v>
       </c>
       <c r="J17" s="20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17" s="20">
-        <v>0.60160000000000002</v>
+        <v>0.52580000000000005</v>
       </c>
       <c r="L17" s="20">
-        <v>0.55400000000000005</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+        <v>0.54700000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H19" s="20" t="s">
+        <v>767</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>791</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>792</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>793</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>794</v>
+      </c>
+    </row>
     <row r="20" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="21" t="s">
         <v>763</v>
@@ -12101,7 +12302,7 @@
         <v>767</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="E20" s="23" t="s">
         <v>793</v>
@@ -12110,11 +12311,21 @@
         <v>805</v>
       </c>
       <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
+      <c r="H20" s="55" t="s">
+        <v>943</v>
+      </c>
+      <c r="I20" s="55" t="s">
+        <v>775</v>
+      </c>
+      <c r="J20" s="55" t="s">
+        <v>944</v>
+      </c>
+      <c r="K20" s="55" t="s">
+        <v>776</v>
+      </c>
+      <c r="L20" s="55" t="s">
+        <v>795</v>
+      </c>
     </row>
     <row r="21" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B21" s="25">
@@ -12128,25 +12339,25 @@
         <f t="array" ref="D21:D35">J21:J35</f>
         <v>4</v>
       </c>
-      <c r="E21" s="58" cm="1">
+      <c r="E21" s="57" cm="1">
         <f t="array" ref="E21:E35">K21:K35*16</f>
-        <v>-12.990399999999999</v>
+        <v>-12.4064</v>
       </c>
       <c r="F21" s="48" cm="1">
         <f t="array" ref="F21:F35">I21:I35*16</f>
-        <v>-3.2480000000000002</v>
+        <v>-3.1023999999999998</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="I21" s="20">
-        <v>-0.20300000000000001</v>
+        <v>-0.19389999999999999</v>
       </c>
       <c r="J21" s="20">
         <v>4</v>
       </c>
       <c r="K21" s="20">
-        <v>-0.81189999999999996</v>
+        <v>-0.77539999999999998</v>
       </c>
       <c r="L21" s="20">
         <v>0.28100000000000003</v>
@@ -12162,26 +12373,26 @@
       <c r="D22" s="32">
         <v>3</v>
       </c>
-      <c r="E22" s="59">
-        <v>-8.8271999999999995</v>
+      <c r="E22" s="58">
+        <v>-9.1584000000000003</v>
       </c>
       <c r="F22" s="49">
-        <v>-2.9424000000000001</v>
+        <v>-3.0528</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="I22" s="20">
-        <v>-0.18390000000000001</v>
+        <v>-0.1908</v>
       </c>
       <c r="J22" s="20">
         <v>3</v>
       </c>
       <c r="K22" s="20">
-        <v>-0.55169999999999997</v>
+        <v>-0.57240000000000002</v>
       </c>
       <c r="L22" s="20">
-        <v>0.29399999999999998</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
@@ -12189,31 +12400,31 @@
         <v>3</v>
       </c>
       <c r="C23" s="43" t="str">
-        <v>J.D. Roberts</v>
+        <v>Scott Linehan</v>
       </c>
       <c r="D23" s="32">
-        <v>4</v>
-      </c>
-      <c r="E23" s="59">
-        <v>-10.430400000000001</v>
+        <v>3</v>
+      </c>
+      <c r="E23" s="58">
+        <v>-8.4976000000000003</v>
       </c>
       <c r="F23" s="49">
-        <v>-2.6080000000000001</v>
+        <v>-2.8319999999999999</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="I23" s="20">
-        <v>-0.16300000000000001</v>
+        <v>-0.17699999999999999</v>
       </c>
       <c r="J23" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="20">
-        <v>-0.65190000000000003</v>
+        <v>-0.53110000000000002</v>
       </c>
       <c r="L23" s="20">
-        <v>0.223</v>
+        <v>0.22900000000000001</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
@@ -12221,31 +12432,31 @@
         <v>4</v>
       </c>
       <c r="C24" s="43" t="str">
-        <v>Scott Linehan</v>
+        <v>Hue Jackson</v>
       </c>
       <c r="D24" s="32">
-        <v>3</v>
-      </c>
-      <c r="E24" s="59">
-        <v>-7.3647999999999998</v>
+        <v>4</v>
+      </c>
+      <c r="E24" s="58">
+        <v>-10.457599999999999</v>
       </c>
       <c r="F24" s="49">
-        <v>-2.4544000000000001</v>
+        <v>-2.6143999999999998</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>842</v>
+        <v>947</v>
       </c>
       <c r="I24" s="20">
-        <v>-0.15340000000000001</v>
+        <v>-0.16339999999999999</v>
       </c>
       <c r="J24" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" s="20">
-        <v>-0.46029999999999999</v>
+        <v>-0.65359999999999996</v>
       </c>
       <c r="L24" s="20">
-        <v>0.27100000000000002</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
@@ -12253,31 +12464,31 @@
         <v>5</v>
       </c>
       <c r="C25" s="43" t="str">
-        <v>Steve Spagnuolo</v>
+        <v>Bruce Coslet</v>
       </c>
       <c r="D25" s="32">
-        <v>3</v>
-      </c>
-      <c r="E25" s="59">
-        <v>-6.3311999999999999</v>
+        <v>8</v>
+      </c>
+      <c r="E25" s="58">
+        <v>-20.076799999999999</v>
       </c>
       <c r="F25" s="49">
-        <v>-2.1103999999999998</v>
+        <v>-2.5087999999999999</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="I25" s="20">
-        <v>-0.13189999999999999</v>
+        <v>-0.15679999999999999</v>
       </c>
       <c r="J25" s="20">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K25" s="20">
-        <v>-0.3957</v>
+        <v>-1.2547999999999999</v>
       </c>
       <c r="L25" s="20">
-        <v>0.20799999999999999</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
@@ -12285,31 +12496,31 @@
         <v>6</v>
       </c>
       <c r="C26" s="43" t="str">
-        <v>June Jones</v>
+        <v>Jack Patera</v>
       </c>
       <c r="D26" s="32">
-        <v>3</v>
-      </c>
-      <c r="E26" s="59">
-        <v>-6.2111999999999998</v>
+        <v>7</v>
+      </c>
+      <c r="E26" s="58">
+        <v>-17.265599999999999</v>
       </c>
       <c r="F26" s="49">
-        <v>-2.0703999999999998</v>
+        <v>-2.4672000000000001</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="I26" s="20">
-        <v>-0.12939999999999999</v>
+        <v>-0.1542</v>
       </c>
       <c r="J26" s="20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K26" s="20">
-        <v>-0.38819999999999999</v>
+        <v>-1.0790999999999999</v>
       </c>
       <c r="L26" s="20">
-        <v>0.39600000000000002</v>
+        <v>0.32100000000000001</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
@@ -12317,31 +12528,31 @@
         <v>7</v>
       </c>
       <c r="C27" s="43" t="str">
-        <v>Paul Wiggin</v>
+        <v>David Shula</v>
       </c>
       <c r="D27" s="32">
-        <v>3</v>
-      </c>
-      <c r="E27" s="59">
-        <v>-6.1824000000000003</v>
+        <v>5</v>
+      </c>
+      <c r="E27" s="58">
+        <v>-12.2064</v>
       </c>
       <c r="F27" s="49">
-        <v>-2.0608</v>
+        <v>-2.4416000000000002</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>840</v>
+        <v>937</v>
       </c>
       <c r="I27" s="20">
-        <v>-0.1288</v>
+        <v>-0.15260000000000001</v>
       </c>
       <c r="J27" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="20">
-        <v>-0.38640000000000002</v>
+        <v>-0.76290000000000002</v>
       </c>
       <c r="L27" s="20">
-        <v>0.28599999999999998</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
@@ -12349,31 +12560,31 @@
         <v>8</v>
       </c>
       <c r="C28" s="43" t="str">
-        <v>Bruce Coslet</v>
+        <v>Kay Stephenson</v>
       </c>
       <c r="D28" s="32">
-        <v>8</v>
-      </c>
-      <c r="E28" s="59">
-        <v>-15.929600000000001</v>
+        <v>3</v>
+      </c>
+      <c r="E28" s="58">
+        <v>-7.2336</v>
       </c>
       <c r="F28" s="49">
-        <v>-1.992</v>
+        <v>-2.4112</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="I28" s="20">
-        <v>-0.1245</v>
+        <v>-0.1507</v>
       </c>
       <c r="J28" s="20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K28" s="20">
-        <v>-0.99560000000000004</v>
+        <v>-0.4521</v>
       </c>
       <c r="L28" s="20">
-        <v>0.34399999999999997</v>
+        <v>0.20799999999999999</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
@@ -12381,31 +12592,31 @@
         <v>9</v>
       </c>
       <c r="C29" s="43" t="str">
-        <v>Abe Gibron</v>
+        <v>J.D. Roberts</v>
       </c>
       <c r="D29" s="32">
         <v>3</v>
       </c>
-      <c r="E29" s="59">
-        <v>-5.8992000000000004</v>
+      <c r="E29" s="58">
+        <v>-6.992</v>
       </c>
       <c r="F29" s="49">
-        <v>-1.9663999999999999</v>
+        <v>-2.3311999999999999</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="I29" s="20">
-        <v>-0.1229</v>
+        <v>-0.1457</v>
       </c>
       <c r="J29" s="20">
         <v>3</v>
       </c>
       <c r="K29" s="20">
-        <v>-0.36870000000000003</v>
+        <v>-0.437</v>
       </c>
       <c r="L29" s="20">
-        <v>0.27400000000000002</v>
+        <v>0.22600000000000001</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
@@ -12418,23 +12629,23 @@
       <c r="D30" s="32">
         <v>3</v>
       </c>
-      <c r="E30" s="59">
-        <v>-5.8639999999999999</v>
+      <c r="E30" s="58">
+        <v>-6.7759999999999998</v>
       </c>
       <c r="F30" s="49">
-        <v>-1.9552</v>
+        <v>-2.2591999999999999</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="I30" s="20">
-        <v>-0.1222</v>
+        <v>-0.14119999999999999</v>
       </c>
       <c r="J30" s="20">
         <v>3</v>
       </c>
       <c r="K30" s="20">
-        <v>-0.36649999999999999</v>
+        <v>-0.42349999999999999</v>
       </c>
       <c r="L30" s="20">
         <v>0.20799999999999999</v>
@@ -12445,31 +12656,31 @@
         <v>11</v>
       </c>
       <c r="C31" s="43" t="str">
-        <v>Joe Bugel</v>
+        <v>Paul Wiggin</v>
       </c>
       <c r="D31" s="32">
-        <v>5</v>
-      </c>
-      <c r="E31" s="59">
-        <v>-9.4255999999999993</v>
+        <v>3</v>
+      </c>
+      <c r="E31" s="58">
+        <v>-6.6239999999999997</v>
       </c>
       <c r="F31" s="49">
-        <v>-1.8848</v>
+        <v>-2.2080000000000002</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I31" s="20">
-        <v>-0.1178</v>
+        <v>-0.13800000000000001</v>
       </c>
       <c r="J31" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K31" s="20">
-        <v>-0.58909999999999996</v>
+        <v>-0.41399999999999998</v>
       </c>
       <c r="L31" s="20">
-        <v>0.3</v>
+        <v>0.28599999999999998</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
@@ -12477,31 +12688,31 @@
         <v>12</v>
       </c>
       <c r="C32" s="43" t="str">
-        <v>Mike Riley</v>
+        <v>Bill Arnsparger</v>
       </c>
       <c r="D32" s="32">
         <v>3</v>
       </c>
-      <c r="E32" s="59">
-        <v>-5.5103999999999997</v>
+      <c r="E32" s="58">
+        <v>-6.1840000000000002</v>
       </c>
       <c r="F32" s="49">
-        <v>-1.8368</v>
+        <v>-2.0608</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>814</v>
+        <v>946</v>
       </c>
       <c r="I32" s="20">
-        <v>-0.1148</v>
+        <v>-0.1288</v>
       </c>
       <c r="J32" s="20">
         <v>3</v>
       </c>
       <c r="K32" s="20">
-        <v>-0.34439999999999998</v>
+        <v>-0.38650000000000001</v>
       </c>
       <c r="L32" s="20">
-        <v>0.29199999999999998</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
@@ -12509,31 +12720,31 @@
         <v>13</v>
       </c>
       <c r="C33" s="43" t="str">
-        <v>Mike McCormack</v>
+        <v>Steve Spagnuolo</v>
       </c>
       <c r="D33" s="32">
-        <v>5</v>
-      </c>
-      <c r="E33" s="59">
-        <v>-9.1519999999999992</v>
+        <v>3</v>
+      </c>
+      <c r="E33" s="58">
+        <v>-6.0448000000000004</v>
       </c>
       <c r="F33" s="49">
-        <v>-1.8304</v>
+        <v>-2.0144000000000002</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>837</v>
+        <v>813</v>
       </c>
       <c r="I33" s="20">
-        <v>-0.1144</v>
+        <v>-0.12590000000000001</v>
       </c>
       <c r="J33" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K33" s="20">
-        <v>-0.57199999999999995</v>
+        <v>-0.37780000000000002</v>
       </c>
       <c r="L33" s="20">
-        <v>0.34799999999999998</v>
+        <v>0.20799999999999999</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
@@ -12541,31 +12752,31 @@
         <v>14</v>
       </c>
       <c r="C34" s="43" t="str">
-        <v>Kay Stephenson</v>
+        <v>Abe Gibron</v>
       </c>
       <c r="D34" s="32">
         <v>3</v>
       </c>
-      <c r="E34" s="59">
-        <v>-5.1984000000000004</v>
+      <c r="E34" s="58">
+        <v>-5.9088000000000003</v>
       </c>
       <c r="F34" s="49">
-        <v>-1.7327999999999999</v>
+        <v>-1.9696</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="I34" s="20">
-        <v>-0.10829999999999999</v>
+        <v>-0.1231</v>
       </c>
       <c r="J34" s="20">
         <v>3</v>
       </c>
       <c r="K34" s="20">
-        <v>-0.32490000000000002</v>
+        <v>-0.36930000000000002</v>
       </c>
       <c r="L34" s="20">
-        <v>0.25</v>
+        <v>0.27400000000000002</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12573,36 +12784,36 @@
         <v>15</v>
       </c>
       <c r="C35" s="44" t="str">
-        <v>Dan Henning</v>
+        <v>June Jones</v>
       </c>
       <c r="D35" s="37">
-        <v>7</v>
-      </c>
-      <c r="E35" s="60">
-        <v>-12.043200000000001</v>
+        <v>3</v>
+      </c>
+      <c r="E35" s="59">
+        <v>-5.8064</v>
       </c>
       <c r="F35" s="50">
-        <v>-1.72</v>
+        <v>-1.9359999999999999</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="I35" s="20">
-        <v>-0.1075</v>
+        <v>-0.121</v>
       </c>
       <c r="J35" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K35" s="20">
-        <v>-0.75270000000000004</v>
+        <v>-0.3629</v>
       </c>
       <c r="L35" s="20">
-        <v>0.34399999999999997</v>
+        <v>0.39600000000000002</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="H20:M20" xr:uid="{F8637A5E-0D6C-48C9-A9D7-A0071E493A12}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:M35">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:L35">
       <sortCondition ref="I20"/>
     </sortState>
   </autoFilter>
@@ -12613,12 +12824,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A52C07A-37FD-4FD9-80F8-E4D4E39D4100}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="B2:K32"/>
+  <dimension ref="A2:V54"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="20"/>
     <col min="2" max="2" width="17.54296875" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" style="57" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" style="56" customWidth="1"/>
     <col min="4" max="4" width="14.54296875" style="40" customWidth="1"/>
     <col min="5" max="7" width="14.54296875" style="20" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" style="40" customWidth="1"/>
@@ -12627,18 +12838,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="88"/>
+      <c r="B2" s="84"/>
       <c r="C2"/>
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
-      <c r="I2" s="89"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" spans="2:9" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61" t="s">
-        <v>845</v>
+      <c r="B3" s="60" t="s">
+        <v>834</v>
       </c>
       <c r="C3" s="23" t="str" cm="1">
         <f t="array" ref="C3:H3">_xlfn.SEQUENCE(1,6,1970,10)&amp;"'s"</f>
@@ -12660,389 +12871,404 @@
         <v>2020's</v>
       </c>
       <c r="I3" s="54" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="28" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="62" t="s">
-        <v>848</v>
-      </c>
-      <c r="C4" s="64" cm="1">
+      <c r="B4" s="61" t="s">
+        <v>837</v>
+      </c>
+      <c r="C4" s="63" cm="1">
         <f t="array" ref="C4:H4">C19:H19</f>
-        <v>-0.35</v>
-      </c>
-      <c r="D4" s="64">
-        <v>0.42</v>
-      </c>
-      <c r="E4" s="64">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="F4" s="64">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G4" s="64">
-        <v>0.25</v>
+        <v>-0.39</v>
+      </c>
+      <c r="D4" s="63">
+        <v>0.47</v>
+      </c>
+      <c r="E4" s="63">
+        <v>-0.33</v>
+      </c>
+      <c r="F4" s="63">
+        <v>0.03</v>
+      </c>
+      <c r="G4" s="63">
+        <v>0.1</v>
       </c>
       <c r="H4" s="45">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="I4" s="65">
+        <v>0.46</v>
+      </c>
+      <c r="I4" s="64">
         <f t="shared" ref="I4:I6" si="0">H4-C4</f>
-        <v>0.91999999999999993</v>
+        <v>0.85000000000000009</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="71" t="s">
-        <v>847</v>
-      </c>
-      <c r="C5" s="103" cm="1">
+      <c r="B5" s="62" t="s">
+        <v>836</v>
+      </c>
+      <c r="C5" s="110" cm="1">
         <f t="array" ref="C5:H5">C18:H18</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="D5" s="103">
-        <v>0.46</v>
-      </c>
-      <c r="E5" s="103">
-        <v>0.19</v>
-      </c>
-      <c r="F5" s="103">
-        <v>0.08</v>
-      </c>
-      <c r="G5" s="103">
-        <v>0.53</v>
-      </c>
-      <c r="H5" s="104">
+        <v>0.51</v>
+      </c>
+      <c r="D5" s="110">
+        <v>0.21</v>
+      </c>
+      <c r="E5" s="110">
+        <v>0.39</v>
+      </c>
+      <c r="F5" s="110">
         <v>0.16</v>
+      </c>
+      <c r="G5" s="110">
+        <v>0.24</v>
+      </c>
+      <c r="H5" s="46">
+        <v>-0.12</v>
       </c>
       <c r="I5" s="46">
         <f t="shared" si="0"/>
-        <v>-0.40999999999999992</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="28" hidden="1" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="100" t="s">
-        <v>849</v>
-      </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="47">
+      <c r="B6" s="96" t="s">
+        <v>838</v>
+      </c>
+      <c r="C6" s="97" cm="1">
+        <f t="array" ref="C6:H6">C20:H20</f>
+        <v>0.13</v>
+      </c>
+      <c r="D6" s="97">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="97">
+        <v>0.6</v>
+      </c>
+      <c r="F6" s="97" t="str">
+        <v>--</v>
+      </c>
+      <c r="G6" s="97" t="str">
+        <v>--</v>
+      </c>
+      <c r="H6" s="98" t="str">
+        <v>--</v>
+      </c>
+      <c r="I6" s="98" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" s="55" customFormat="1" ht="28" customHeight="1" collapsed="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="94" t="s">
-        <v>936</v>
-      </c>
-      <c r="C7" s="90" t="str" cm="1">
-        <f t="array" ref="C7:H7">TRIM(_xlfn.TEXTBEFORE(TRANSPOSE(C27:C32),"coaches"))</f>
-        <v>38/24</v>
-      </c>
-      <c r="D7" s="90" t="str">
-        <v>32/19</v>
-      </c>
-      <c r="E7" s="90" t="str">
-        <v>38/25</v>
-      </c>
-      <c r="F7" s="90" t="str">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" s="55" customFormat="1" ht="28" customHeight="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="90" t="s">
+        <v>901</v>
+      </c>
+      <c r="C7" s="86" t="str" cm="1">
+        <f t="array" ref="C7:H7">F46:K46</f>
+        <v>34/21</v>
+      </c>
+      <c r="D7" s="86" t="str">
+        <v>30/22</v>
+      </c>
+      <c r="E7" s="86" t="str">
+        <v>33/28</v>
+      </c>
+      <c r="F7" s="86" t="str">
+        <v>40/37</v>
+      </c>
+      <c r="G7" s="86" t="str">
         <v>42/33</v>
       </c>
-      <c r="G7" s="90" t="str">
-        <v>44/32</v>
-      </c>
-      <c r="H7" s="95" t="str">
-        <v>33/22</v>
-      </c>
-      <c r="I7" s="91"/>
+      <c r="H7" s="91" t="str">
+        <v>33/20</v>
+      </c>
+      <c r="I7" s="87"/>
     </row>
     <row r="8" spans="2:9" s="55" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="96" t="str">
+      <c r="B8" s="92" t="str">
         <f>SUBSTITUTE(B7,"Coaches", "Seasons")</f>
         <v>Sample Size, Seasons (O/D)</v>
       </c>
-      <c r="C8" s="97" t="str" cm="1">
-        <f t="array" ref="C8:H8">TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(TRANSPOSE(C27:C32),","),"seasons"))</f>
-        <v>95/101</v>
-      </c>
-      <c r="D8" s="97" t="str">
-        <v>149/76</v>
-      </c>
-      <c r="E8" s="97" t="str">
-        <v>163/102</v>
-      </c>
-      <c r="F8" s="97" t="str">
-        <v>165/122</v>
-      </c>
-      <c r="G8" s="97" t="str">
-        <v>163/126</v>
-      </c>
-      <c r="H8" s="98" t="str">
-        <v>91/61</v>
-      </c>
-      <c r="I8" s="99"/>
+      <c r="C8" s="93" t="str" cm="1">
+        <f t="array" ref="C8:H8">F47:K47</f>
+        <v>87/82</v>
+      </c>
+      <c r="D8" s="93" t="str">
+        <v>146/83</v>
+      </c>
+      <c r="E8" s="93" t="str">
+        <v>143/126</v>
+      </c>
+      <c r="F8" s="93" t="str">
+        <v>152/151</v>
+      </c>
+      <c r="G8" s="93" t="str">
+        <v>158/135</v>
+      </c>
+      <c r="H8" s="94" t="str">
+        <v>92/56</v>
+      </c>
+      <c r="I8" s="95"/>
     </row>
     <row r="9" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="78" t="str" cm="1">
+      <c r="B9" s="74" t="str" cm="1">
         <f t="array" ref="B9:B10">TRIM(TRANSPOSE(D24:E24))</f>
         <v>Mean WAR (O/D)</v>
       </c>
       <c r="C9" s="32" t="str" cm="1">
-        <f t="array" ref="C9:H10">TRIM(TRANSPOSE(D27:E32))</f>
-        <v>-0.355 / +0.573</v>
+        <f t="array" ref="C9:H9">E54:J54</f>
+        <v>-0.39 / 0.513</v>
       </c>
       <c r="D9" s="32" t="str">
-        <v>+0.421 / +0.456</v>
+        <v>0.472 / 0.214</v>
       </c>
       <c r="E9" s="32" t="str">
-        <v>-0.140 / +0.193</v>
+        <v>-0.329 / 0.389</v>
       </c>
       <c r="F9" s="32" t="str">
-        <v>+0.139 / +0.076</v>
+        <v>0.029 / 0.156</v>
       </c>
       <c r="G9" s="32" t="str">
-        <v>+0.246 / +0.528</v>
+        <v>0.1 / 0.243</v>
       </c>
       <c r="H9" s="34" t="str">
-        <v>+0.572 / +0.156</v>
-      </c>
-      <c r="I9" s="92"/>
+        <v>0.46 / -0.116</v>
+      </c>
+      <c r="I9" s="88"/>
     </row>
     <row r="10" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="78" t="str">
+      <c r="B10" s="74" t="str">
         <v>Difference (O - D)</v>
       </c>
-      <c r="C10" s="32" t="str">
-        <v>-0.927</v>
-      </c>
-      <c r="D10" s="32" t="str">
-        <v>-0.035</v>
-      </c>
-      <c r="E10" s="32" t="str">
-        <v>-0.333</v>
-      </c>
-      <c r="F10" s="32" t="str">
-        <v>0.063</v>
-      </c>
-      <c r="G10" s="32" t="str">
-        <v>-0.282</v>
-      </c>
-      <c r="H10" s="34" t="str">
-        <v>0.416</v>
-      </c>
-      <c r="I10" s="92"/>
+      <c r="C10" s="32" cm="1">
+        <f t="array" ref="C10:H10">F49:K49</f>
+        <v>-0.90400000000000003</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="E10" s="32">
+        <v>-0.71799999999999997</v>
+      </c>
+      <c r="F10" s="32">
+        <v>-0.127</v>
+      </c>
+      <c r="G10" s="32">
+        <v>-0.14299999999999999</v>
+      </c>
+      <c r="H10" s="34">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="I10" s="88"/>
     </row>
     <row r="11" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="78" t="str" cm="1">
+      <c r="B11" s="74" t="str" cm="1">
         <f t="array" ref="B11:B12">TRANSPOSE(J24:K24)</f>
         <v>U-statistic</v>
       </c>
       <c r="C11" s="32" cm="1">
-        <f t="array" ref="C11:H12">TRANSPOSE(J27:K32)</f>
-        <v>3290</v>
+        <f t="array" ref="C11:H12">C50:H51</f>
+        <v>2626</v>
       </c>
       <c r="D11" s="32">
-        <v>5389</v>
+        <v>6272</v>
       </c>
       <c r="E11" s="32">
-        <v>7553</v>
+        <v>7144</v>
       </c>
       <c r="F11" s="32">
-        <v>10275</v>
+        <v>11082</v>
       </c>
       <c r="G11" s="32">
-        <v>9430</v>
+        <v>10192</v>
       </c>
       <c r="H11" s="34">
-        <v>3151</v>
-      </c>
-      <c r="I11" s="92"/>
+        <v>2979</v>
+      </c>
+      <c r="I11" s="88"/>
     </row>
     <row r="12" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="78" t="str">
+      <c r="B12" s="74" t="str">
         <v>p-value</v>
       </c>
       <c r="C12" s="32">
-        <v>1E-4</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="D12" s="32">
-        <v>0.55500000000000005</v>
+        <v>0.6593</v>
       </c>
       <c r="E12" s="32">
-        <v>0.21099999999999999</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="F12" s="32">
-        <v>0.76300000000000001</v>
+        <v>0.60580000000000001</v>
       </c>
       <c r="G12" s="32">
-        <v>0.23400000000000001</v>
+        <v>0.51339999999999997</v>
       </c>
       <c r="H12" s="34">
-        <v>0.159</v>
-      </c>
-      <c r="I12" s="92"/>
+        <v>0.1115</v>
+      </c>
+      <c r="I12" s="88"/>
     </row>
     <row r="13" spans="2:9" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="83" t="str">
+      <c r="B13" s="79" t="str">
         <f>TRIM(H24)</f>
         <v>Significance</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>934</v>
+        <v>899</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>935</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>935</v>
+        <v>900</v>
+      </c>
+      <c r="E13" s="37" t="str">
+        <f>C13</f>
+        <v>Highly Significant</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>935</v>
+        <v>900</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>935</v>
+        <v>900</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>935</v>
-      </c>
-      <c r="I13" s="93"/>
+        <v>900</v>
+      </c>
+      <c r="I13" s="89"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="20" t="s">
-        <v>846</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>850</v>
+        <v>835</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>839</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="20" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B18" s="20" t="s">
-        <v>847</v>
-      </c>
-      <c r="C18" s="57">
-        <v>0.56999999999999995</v>
+        <v>836</v>
+      </c>
+      <c r="C18" s="56">
+        <v>0.51</v>
       </c>
       <c r="D18" s="40">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
       <c r="E18" s="20">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="F18" s="20">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="G18" s="20">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="H18" s="40">
-        <v>0.16</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B19" s="20" t="s">
-        <v>848</v>
-      </c>
-      <c r="C19" s="57">
-        <v>-0.35</v>
+        <v>837</v>
+      </c>
+      <c r="C19" s="56">
+        <v>-0.39</v>
       </c>
       <c r="D19" s="40">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="E19" s="20">
-        <v>-0.14000000000000001</v>
+        <v>-0.33</v>
       </c>
       <c r="F19" s="20">
-        <v>0.14000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="G19" s="20">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="H19" s="40">
-        <v>0.56999999999999995</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="20" t="s">
-        <v>849</v>
-      </c>
-      <c r="C20" s="57">
-        <v>0.02</v>
+        <v>838</v>
+      </c>
+      <c r="C20" s="56">
+        <v>0.13</v>
       </c>
       <c r="D20" s="40">
-        <v>-0.11</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="F20" s="20">
-        <v>0.04</v>
-      </c>
-      <c r="G20" s="20">
-        <v>0.43</v>
-      </c>
-      <c r="H20" s="40">
-        <v>-7.0000000000000007E-2</v>
+        <v>0.6</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="24" spans="2:11" s="55" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B24" s="67" t="s">
-        <v>887</v>
-      </c>
-      <c r="C24" s="68" t="s">
-        <v>888</v>
+      <c r="B24" s="66" t="s">
+        <v>852</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>853</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>889</v>
+        <v>854</v>
       </c>
       <c r="E24" s="55" t="s">
-        <v>931</v>
+        <v>896</v>
       </c>
       <c r="F24" s="55" t="s">
-        <v>890</v>
-      </c>
-      <c r="G24" s="68" t="s">
-        <v>891</v>
-      </c>
-      <c r="H24" s="68" t="s">
-        <v>892</v>
-      </c>
-      <c r="I24" s="68"/>
+        <v>855</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>856</v>
+      </c>
+      <c r="H24" s="67" t="s">
+        <v>857</v>
+      </c>
+      <c r="I24" s="67"/>
       <c r="J24" s="55" t="s">
-        <v>932</v>
+        <v>897</v>
       </c>
       <c r="K24" s="55" t="s">
-        <v>933</v>
+        <v>898</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B25" s="57" t="s">
-        <v>893</v>
+      <c r="B25" s="56" t="s">
+        <v>858</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>894</v>
+        <v>859</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>778</v>
@@ -13051,59 +13277,59 @@
         <v>795</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>895</v>
+        <v>860</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>896</v>
+        <v>861</v>
       </c>
       <c r="H25" s="40" t="s">
-        <v>897</v>
+        <v>862</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B26" s="57" t="s">
-        <v>898</v>
+      <c r="B26" s="56" t="s">
+        <v>863</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>899</v>
+        <v>864</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>900</v>
+        <v>865</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>901</v>
+        <v>866</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>902</v>
+        <v>867</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>903</v>
+        <v>868</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>904</v>
+        <v>869</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B27" s="57" t="s">
-        <v>905</v>
+      <c r="B27" s="56" t="s">
+        <v>870</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>925</v>
+        <v>890</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>906</v>
+        <v>871</v>
       </c>
       <c r="E27" s="20">
         <v>-0.92700000000000005</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>907</v>
+        <v>872</v>
       </c>
       <c r="G27" s="40">
         <v>-0.53200000000000003</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>908</v>
+        <v>873</v>
       </c>
       <c r="J27" s="20" cm="1">
         <f t="array" ref="J27:J32">VALUE(_xlfn.TEXTBEFORE(F27:F32,"p"))</f>
@@ -13115,26 +13341,26 @@
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B28" s="57" t="s">
-        <v>909</v>
+      <c r="B28" s="56" t="s">
+        <v>874</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>926</v>
+        <v>891</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>910</v>
+        <v>875</v>
       </c>
       <c r="E28" s="20">
         <v>-3.5000000000000003E-2</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>911</v>
+        <v>876</v>
       </c>
       <c r="G28" s="40">
         <v>-1.9E-2</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="J28" s="20">
         <v>5389</v>
@@ -13144,26 +13370,26 @@
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B29" s="57" t="s">
-        <v>913</v>
+      <c r="B29" s="56" t="s">
+        <v>878</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>927</v>
+        <v>892</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>914</v>
+        <v>879</v>
       </c>
       <c r="E29" s="20">
         <v>-0.33300000000000002</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>915</v>
+        <v>880</v>
       </c>
       <c r="G29" s="40">
         <v>-0.17399999999999999</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="J29" s="20">
         <v>7553</v>
@@ -13173,26 +13399,26 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B30" s="57" t="s">
-        <v>916</v>
+      <c r="B30" s="56" t="s">
+        <v>881</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>928</v>
+        <v>893</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>917</v>
+        <v>882</v>
       </c>
       <c r="E30" s="20">
         <v>6.3E-2</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>918</v>
+        <v>883</v>
       </c>
       <c r="G30" s="40">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="H30" s="40" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="J30" s="20">
         <v>10275</v>
@@ -13202,26 +13428,26 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B31" s="57" t="s">
-        <v>919</v>
+      <c r="B31" s="56" t="s">
+        <v>884</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>929</v>
+        <v>894</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>920</v>
+        <v>885</v>
       </c>
       <c r="E31" s="20">
         <v>-0.28199999999999997</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>921</v>
+        <v>886</v>
       </c>
       <c r="G31" s="40">
         <v>-0.151</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="J31" s="20">
         <v>9430</v>
@@ -13231,32 +13457,550 @@
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B32" s="57" t="s">
-        <v>922</v>
+      <c r="B32" s="56" t="s">
+        <v>887</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>930</v>
+        <v>895</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>923</v>
+        <v>888</v>
       </c>
       <c r="E32" s="20">
         <v>0.41599999999999998</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>924</v>
+        <v>889</v>
       </c>
       <c r="G32" s="40">
         <v>0.25700000000000001</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="J32" s="20">
         <v>3151</v>
       </c>
       <c r="K32" s="20">
         <v>0.159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>948</v>
+      </c>
+      <c r="B35" s="56" t="str" cm="1">
+        <f t="array" ref="B35:B38">TRIM(_xlfn.TEXTAFTER(A35:A38,")"))</f>
+        <v>38/24 32/19 38/25 42/33 44/32 33/22</v>
+      </c>
+      <c r="C35" s="56" t="str" cm="1">
+        <f t="array" ref="C35:H35">_xlfn.TEXTSPLIT(B35," ")</f>
+        <v>38/24</v>
+      </c>
+      <c r="D35" s="40" t="str">
+        <v>32/19</v>
+      </c>
+      <c r="E35" s="20" t="str">
+        <v>38/25</v>
+      </c>
+      <c r="F35" s="20" t="str">
+        <v>42/33</v>
+      </c>
+      <c r="G35" s="20" t="str">
+        <v>44/32</v>
+      </c>
+      <c r="H35" s="40" t="str">
+        <v>33/22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A36" s="20" t="s">
+        <v>949</v>
+      </c>
+      <c r="B36" s="56" t="str">
+        <v>95/102 149/76 163/102 165/122 163/126 91/61</v>
+      </c>
+      <c r="C36" s="56" t="str" cm="1">
+        <f t="array" ref="C36:H36">_xlfn.TEXTSPLIT(B36," ")</f>
+        <v>95/102</v>
+      </c>
+      <c r="D36" s="40" t="str">
+        <v>149/76</v>
+      </c>
+      <c r="E36" s="20" t="str">
+        <v>163/102</v>
+      </c>
+      <c r="F36" s="20" t="str">
+        <v>165/122</v>
+      </c>
+      <c r="G36" s="20" t="str">
+        <v>163/126</v>
+      </c>
+      <c r="H36" s="40" t="str">
+        <v>91/61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A37" s="20" t="s">
+        <v>950</v>
+      </c>
+      <c r="B37" s="56" t="str">
+        <v>-0.453 / +0.602 +0.441 / +0.368 -0.187 / +0.235 +0.056 / +0.091 +0.048 / +0.369 +0.434 / +0.059</v>
+      </c>
+      <c r="C37" s="56" t="str" cm="1">
+        <f t="array" ref="C37:T37">_xlfn.TEXTSPLIT(B37," ")</f>
+        <v>-0.453</v>
+      </c>
+      <c r="D37" s="40" t="str">
+        <v>/</v>
+      </c>
+      <c r="E37" s="20" t="str">
+        <v>+0.602</v>
+      </c>
+      <c r="F37" s="20" t="str">
+        <v>+0.441</v>
+      </c>
+      <c r="G37" s="20" t="str">
+        <v>/</v>
+      </c>
+      <c r="H37" s="40" t="str">
+        <v>+0.368</v>
+      </c>
+      <c r="I37" s="40" t="str">
+        <v>-0.187</v>
+      </c>
+      <c r="J37" s="20" t="str">
+        <v>/</v>
+      </c>
+      <c r="K37" s="20" t="str">
+        <v>+0.235</v>
+      </c>
+      <c r="L37" s="20" t="str">
+        <v>+0.056</v>
+      </c>
+      <c r="M37" s="20" t="str">
+        <v>/</v>
+      </c>
+      <c r="N37" s="20" t="str">
+        <v>+0.091</v>
+      </c>
+      <c r="O37" s="20" t="str">
+        <v>+0.048</v>
+      </c>
+      <c r="P37" s="20" t="str">
+        <v>/</v>
+      </c>
+      <c r="Q37" s="20" t="str">
+        <v>+0.369</v>
+      </c>
+      <c r="R37" s="20" t="str">
+        <v>+0.434</v>
+      </c>
+      <c r="S37" s="20" t="str">
+        <v>/</v>
+      </c>
+      <c r="T37" s="20" t="str">
+        <v>+0.059</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A38" s="20" t="s">
+        <v>951</v>
+      </c>
+      <c r="B38" s="56" t="str">
+        <v>-1.055 +0.073 -0.422 -0.034 -0.321 +0.375</v>
+      </c>
+      <c r="C38" s="56" t="str" cm="1">
+        <f t="array" ref="C38:H38">_xlfn.TEXTSPLIT(B38," ")</f>
+        <v>-1.055</v>
+      </c>
+      <c r="D38" s="40" t="str">
+        <v>+0.073</v>
+      </c>
+      <c r="E38" s="20" t="str">
+        <v>-0.422</v>
+      </c>
+      <c r="F38" s="20" t="str">
+        <v>-0.034</v>
+      </c>
+      <c r="G38" s="20" t="str">
+        <v>-0.321</v>
+      </c>
+      <c r="H38" s="40" t="str">
+        <v>+0.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A39" s="20" t="s">
+        <v>952</v>
+      </c>
+      <c r="B39" s="56" t="str" cm="1">
+        <f t="array" ref="B39:B41">TRIM(_xlfn.TEXTAFTER(A39:A41," "))</f>
+        <v>3351 5488 7392 9989 9283 3080</v>
+      </c>
+      <c r="C39" s="56" t="str" cm="1">
+        <f t="array" ref="C39:H39">_xlfn.TEXTSPLIT(B39," ")</f>
+        <v>3351</v>
+      </c>
+      <c r="D39" s="40" t="str">
+        <v>5488</v>
+      </c>
+      <c r="E39" s="20" t="str">
+        <v>7392</v>
+      </c>
+      <c r="F39" s="20" t="str">
+        <v>9989</v>
+      </c>
+      <c r="G39" s="20" t="str">
+        <v>9283</v>
+      </c>
+      <c r="H39" s="40" t="str">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A40" s="20" t="s">
+        <v>953</v>
+      </c>
+      <c r="B40" s="56" t="str">
+        <v>0.0002 0.7071 0.1294 0.9135 0.1619 0.2532</v>
+      </c>
+      <c r="C40" s="56" t="str" cm="1">
+        <f t="array" ref="C40:H40">_xlfn.TEXTSPLIT(B40," ")</f>
+        <v>0.0002</v>
+      </c>
+      <c r="D40" s="40" t="str">
+        <v>0.7071</v>
+      </c>
+      <c r="E40" s="20" t="str">
+        <v>0.1294</v>
+      </c>
+      <c r="F40" s="20" t="str">
+        <v>0.9135</v>
+      </c>
+      <c r="G40" s="20" t="str">
+        <v>0.1619</v>
+      </c>
+      <c r="H40" s="40" t="str">
+        <v>0.2532</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A41" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="B41" s="56" t="str">
+        <v>Highly Significant - - - - -</v>
+      </c>
+      <c r="C41" s="56" t="str" cm="1">
+        <f t="array" ref="C41:I41">_xlfn.TEXTSPLIT(B41," ")</f>
+        <v>Highly</v>
+      </c>
+      <c r="D41" s="40" t="str">
+        <v>Significant</v>
+      </c>
+      <c r="E41" s="20" t="str">
+        <v>-</v>
+      </c>
+      <c r="F41" s="20" t="str">
+        <v>-</v>
+      </c>
+      <c r="G41" s="20" t="str">
+        <v>-</v>
+      </c>
+      <c r="H41" s="40" t="str">
+        <v>-</v>
+      </c>
+      <c r="I41" s="40" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="C43" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,C37:E37)</f>
+        <v>-0.453 / +0.602</v>
+      </c>
+      <c r="D43" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,F37:H37)</f>
+        <v>+0.441 / +0.368</v>
+      </c>
+      <c r="E43" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,I37:K37)</f>
+        <v>-0.187 / +0.235</v>
+      </c>
+      <c r="F43" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,L37:N37)</f>
+        <v>+0.056 / +0.091</v>
+      </c>
+      <c r="G43" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,O37:Q37)</f>
+        <v>+0.048 / +0.369</v>
+      </c>
+      <c r="H43" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,R37:T37)</f>
+        <v>+0.434 / +0.059</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B46" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>957</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>958</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>959</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>960</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>961</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>962</v>
+      </c>
+      <c r="I46" s="40" t="s">
+        <v>963</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>964</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B47" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="C47" s="56" t="s">
+        <v>957</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>792</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>959</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>966</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>967</v>
+      </c>
+      <c r="H47" s="40" t="s">
+        <v>968</v>
+      </c>
+      <c r="I47" s="40" t="s">
+        <v>969</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>970</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B48" s="20" t="s">
+        <v>972</v>
+      </c>
+      <c r="C48" s="56" t="s">
+        <v>770</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>959</v>
+      </c>
+      <c r="E48" s="20">
+        <v>-0.39</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="G48" s="20">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="H48" s="40">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="I48" s="40" t="s">
+        <v>973</v>
+      </c>
+      <c r="J48" s="20">
+        <v>0.214</v>
+      </c>
+      <c r="K48" s="20">
+        <v>-0.32900000000000001</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="M48" s="20">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="N48" s="20">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="P48" s="20">
+        <v>0.156</v>
+      </c>
+      <c r="Q48" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="R48" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="S48" s="20">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="T48" s="20">
+        <v>0.46</v>
+      </c>
+      <c r="U48" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="V48" s="20">
+        <v>-0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B49" s="20" t="s">
+        <v>850</v>
+      </c>
+      <c r="C49" s="56" t="s">
+        <v>974</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>900</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>975</v>
+      </c>
+      <c r="F49" s="20">
+        <v>-0.90400000000000003</v>
+      </c>
+      <c r="G49" s="20">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="H49" s="40">
+        <v>-0.71799999999999997</v>
+      </c>
+      <c r="I49" s="40">
+        <v>-0.127</v>
+      </c>
+      <c r="J49" s="20">
+        <v>-0.14299999999999999</v>
+      </c>
+      <c r="K49" s="20">
+        <v>0.57599999999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B50" s="20" t="s">
+        <v>897</v>
+      </c>
+      <c r="C50" s="56">
+        <v>2626</v>
+      </c>
+      <c r="D50" s="40">
+        <v>6272</v>
+      </c>
+      <c r="E50" s="20">
+        <v>7144</v>
+      </c>
+      <c r="F50" s="20">
+        <v>11082</v>
+      </c>
+      <c r="G50" s="20">
+        <v>10192</v>
+      </c>
+      <c r="H50" s="40">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B51" s="20" t="s">
+        <v>898</v>
+      </c>
+      <c r="C51" s="56">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="D51" s="40">
+        <v>0.6593</v>
+      </c>
+      <c r="E51" s="20">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="F51" s="20">
+        <v>0.60580000000000001</v>
+      </c>
+      <c r="G51" s="20">
+        <v>0.51339999999999997</v>
+      </c>
+      <c r="H51" s="40">
+        <v>0.1115</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B52" s="20" t="s">
+        <v>976</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>977</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>978</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>900</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>977</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>978</v>
+      </c>
+      <c r="H52" s="40" t="s">
+        <v>900</v>
+      </c>
+      <c r="I52" s="40" t="s">
+        <v>900</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E54" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,E48:G48)</f>
+        <v>-0.39 / 0.513</v>
+      </c>
+      <c r="F54" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,H48:J48)</f>
+        <v>0.472 / 0.214</v>
+      </c>
+      <c r="G54" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,K48:M48)</f>
+        <v>-0.329 / 0.389</v>
+      </c>
+      <c r="H54" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,N48:P48)</f>
+        <v>0.029 / 0.156</v>
+      </c>
+      <c r="I54" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,Q48:S48)</f>
+        <v>0.1 / 0.243</v>
+      </c>
+      <c r="J54" s="56" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,T48:V48)</f>
+        <v>0.46 / -0.116</v>
       </c>
     </row>
   </sheetData>
@@ -13266,12 +14010,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A2CB53-2941-4642-9382-91358B7FAA54}">
-  <dimension ref="B2:I26"/>
+  <dimension ref="B2:K26"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="20"/>
     <col min="2" max="2" width="13" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" style="57" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" style="56" customWidth="1"/>
     <col min="4" max="4" width="9.08984375" style="40" customWidth="1"/>
     <col min="5" max="7" width="9.08984375" style="20" customWidth="1"/>
     <col min="8" max="8" width="19.453125" style="40" bestFit="1" customWidth="1"/>
@@ -13279,7 +14023,7 @@
     <col min="10" max="16384" width="8.7265625" style="20"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C2"/>
       <c r="D2"/>
       <c r="E2"/>
@@ -13288,349 +14032,340 @@
       <c r="H2"/>
       <c r="I2"/>
     </row>
-    <row r="3" spans="2:9" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="66" t="s">
-        <v>845</v>
-      </c>
-      <c r="C3" s="52" t="str" cm="1">
-        <f t="array" ref="C3:G3">D16:H16</f>
-        <v xml:space="preserve"> Coaches </v>
-      </c>
-      <c r="D3" s="52" t="str">
-        <v xml:space="preserve"> Seasons </v>
-      </c>
-      <c r="E3" s="52" t="str">
-        <v xml:space="preserve"> Mean WAR </v>
-      </c>
-      <c r="F3" s="52" t="str">
-        <v xml:space="preserve"> Median WAR </v>
-      </c>
-      <c r="G3" s="72" t="str">
-        <v xml:space="preserve"> Std Dev </v>
-      </c>
-      <c r="H3" s="75" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="62" t="s">
+    <row r="3" spans="2:11" s="55" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="65" t="s">
+        <v>834</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>958</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>792</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>982</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>983</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>984</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="61" t="s">
+        <v>836</v>
+      </c>
+      <c r="C4" s="68" cm="1">
+        <f t="array" ref="C4:D5">D18:E19</f>
+        <v>98</v>
+      </c>
+      <c r="D4" s="68">
+        <v>633</v>
+      </c>
+      <c r="E4" s="63" cm="1">
+        <f t="array" ref="E4:E5">F18:F19</f>
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="63" cm="1">
+        <f t="array" ref="F4:F5">H18:H19</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G4" s="126" cm="1">
+        <f t="array" ref="G4:G5">J18:J19</f>
+        <v>1.9</v>
+      </c>
+      <c r="H4" s="72"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="62" t="s">
+        <v>837</v>
+      </c>
+      <c r="C5" s="69">
+        <v>134</v>
+      </c>
+      <c r="D5" s="69">
+        <v>778</v>
+      </c>
+      <c r="E5" s="110">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="110">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="127">
+        <v>1.92</v>
+      </c>
+      <c r="H5" s="73"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="62" t="s">
+        <v>850</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>900</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>900</v>
+      </c>
+      <c r="E6" s="110">
+        <f>-F20</f>
+        <v>-0.19</v>
+      </c>
+      <c r="F6" s="110">
+        <f>-H20</f>
+        <v>-0.25</v>
+      </c>
+      <c r="G6" s="127" t="s">
+        <v>900</v>
+      </c>
+      <c r="H6" s="73"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B7" s="74" t="str" cm="1">
+        <f t="array" ref="B7:B10">TRIM(TRANSPOSE(D23:G23))</f>
+        <v>U</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="34" t="str">
+        <f>"U = "&amp;TEXT(E24,"###,###")</f>
+        <v>U = 231,706</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B8" s="74" t="str">
+        <v>test</v>
+      </c>
+      <c r="C8" s="75"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="34">
+        <f>E25</f>
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="74" t="str">
+        <v>(All</v>
+      </c>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="34" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="15" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="79" t="str">
+        <v>Seasons):</v>
+      </c>
+      <c r="C10" s="80"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(" ",,E26:F26)</f>
+        <v>Marginally significant</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" s="55" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="55" t="s">
         <v>847</v>
       </c>
-      <c r="C4" s="69" cm="1">
-        <f t="array" ref="C4:G4">D19:H19</f>
-        <v>112</v>
-      </c>
-      <c r="D4" s="69">
-        <v>639</v>
-      </c>
-      <c r="E4" s="28">
-        <v>1.52E-2</v>
-      </c>
-      <c r="F4" s="28">
-        <v>1.8499999999999999E-2</v>
-      </c>
-      <c r="G4" s="73">
-        <v>0.1111</v>
-      </c>
-      <c r="H4" s="76"/>
-      <c r="I4" s="20"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="63" t="s">
-        <v>848</v>
-      </c>
-      <c r="C5" s="70" cm="1">
-        <f t="array" ref="C5:G5">D18:H18</f>
-        <v>154</v>
-      </c>
-      <c r="D5" s="70">
-        <v>860</v>
-      </c>
-      <c r="E5" s="33">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="F5" s="33">
-        <v>2.3E-3</v>
-      </c>
-      <c r="G5" s="74">
-        <v>0.1134</v>
-      </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="20"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="63" t="s">
-        <v>884</v>
-      </c>
-      <c r="C6" s="70" cm="1">
-        <f t="array" ref="C6:G6">_xlfn.ANCHORARRAY(C5)-_xlfn.ANCHORARRAY(C4)</f>
-        <v>42</v>
-      </c>
-      <c r="D6" s="70">
-        <v>221</v>
-      </c>
-      <c r="E6" s="33">
-        <v>-9.7000000000000003E-3</v>
-      </c>
-      <c r="F6" s="33">
-        <v>-1.6199999999999999E-2</v>
-      </c>
-      <c r="G6" s="74">
-        <v>2.2999999999999965E-3</v>
-      </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B7" s="78" t="str" cm="1">
-        <f t="array" ref="B7:B10">TRIM(TRANSPOSE(D23:G23))</f>
-        <v>Test Statistic</v>
-      </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="34" t="str" cm="1">
-        <f t="array" ref="H7:H10">TRIM(TRANSPOSE(D26:G26))</f>
-        <v>U = 260,162</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B8" s="78" t="str">
-        <v>p-value</v>
-      </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="34" t="str">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="78" t="str">
-        <v>Effect Size</v>
-      </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="34" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="15" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="83" t="str">
-        <v>Interpretation</v>
-      </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="39" t="str">
-        <v>Marginally significant</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" s="55" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="55" t="s">
-        <v>863</v>
-      </c>
-      <c r="C16" s="67" t="s">
-        <v>874</v>
-      </c>
-      <c r="D16" s="68" t="s">
-        <v>875</v>
+      <c r="C16" s="66" t="s">
+        <v>834</v>
+      </c>
+      <c r="D16" s="67" t="s">
+        <v>958</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>876</v>
+        <v>792</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>877</v>
+        <v>972</v>
       </c>
       <c r="G16" s="55" t="s">
-        <v>878</v>
-      </c>
-      <c r="H16" s="68" t="s">
-        <v>879</v>
-      </c>
-      <c r="I16" s="68"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+      <c r="H16" s="67" t="s">
+        <v>979</v>
+      </c>
+      <c r="I16" s="67" t="s">
+        <v>770</v>
+      </c>
+      <c r="J16" s="55" t="s">
+        <v>980</v>
+      </c>
+      <c r="K16" s="55" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>795</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>775</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>775</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>807</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>795</v>
-      </c>
-      <c r="H17" s="40" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+        <v>847</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>880</v>
+        <v>847</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>836</v>
       </c>
       <c r="D18" s="40">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="E18" s="20">
-        <v>860</v>
+        <v>633</v>
       </c>
       <c r="F18" s="20">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="G18" s="20">
-        <v>2.3E-3</v>
+        <v>0.25</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>986</v>
       </c>
       <c r="H18" s="40">
-        <v>0.1134</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>986</v>
+      </c>
+      <c r="J18" s="20">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>881</v>
+        <v>847</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>837</v>
       </c>
       <c r="D19" s="40">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="E19" s="20">
-        <v>639</v>
+        <v>778</v>
       </c>
       <c r="F19" s="20">
-        <v>1.52E-2</v>
-      </c>
-      <c r="G19" s="20">
-        <v>1.8499999999999999E-2</v>
+        <v>0.06</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>986</v>
       </c>
       <c r="H19" s="40">
-        <v>0.1111</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+        <v>0.04</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>986</v>
+      </c>
+      <c r="J19" s="20">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>882</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>883</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>883</v>
+        <v>847</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>850</v>
+      </c>
+      <c r="D20" s="40">
+        <v>-36</v>
+      </c>
+      <c r="E20" s="20">
+        <v>-145</v>
       </c>
       <c r="F20" s="20">
-        <v>-9.5999999999999992E-3</v>
-      </c>
-      <c r="G20" s="20">
-        <v>-1.6199999999999999E-2</v>
-      </c>
-      <c r="H20" s="40" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" s="55" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>986</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.25</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>986</v>
+      </c>
+      <c r="J20" s="20">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" s="55" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B23" s="55" t="s">
-        <v>857</v>
-      </c>
-      <c r="C23" s="67" t="s">
-        <v>858</v>
-      </c>
-      <c r="D23" s="68" t="s">
-        <v>859</v>
+        <v>846</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>987</v>
+      </c>
+      <c r="D23" s="67" t="s">
+        <v>988</v>
       </c>
       <c r="E23" s="55" t="s">
-        <v>860</v>
+        <v>989</v>
       </c>
       <c r="F23" s="55" t="s">
-        <v>861</v>
+        <v>990</v>
       </c>
       <c r="G23" s="55" t="s">
-        <v>862</v>
-      </c>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+        <v>991</v>
+      </c>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>864</v>
+        <v>847</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>865</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>775</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>866</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+        <v>992</v>
+      </c>
+      <c r="E24" s="128">
+        <v>231706</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>868</v>
+        <v>993</v>
       </c>
       <c r="E25" s="20">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>869</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>872</v>
-      </c>
-      <c r="E26" s="20">
-        <v>7.8E-2</v>
+        <v>994</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>995</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>873</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>885</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -13676,14 +14411,14 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="28.5" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="102" t="str">
         <v>Temporal Holdout (2020-2024)</v>
       </c>
-      <c r="C3" s="105" t="str">
+      <c r="C3" s="99" t="str">
         <v>1,523 seasons 
 (1970-2019)</v>
       </c>
-      <c r="D3" s="105" t="str">
+      <c r="D3" s="99" t="str">
         <v>160 seasons
 (2020-2024)</v>
       </c>
@@ -13701,14 +14436,14 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="28" x14ac:dyDescent="0.35">
-      <c r="B4" s="109" t="str">
+      <c r="B4" s="103" t="str">
         <v>Holdout Coaches</v>
       </c>
-      <c r="C4" s="106" t="str">
+      <c r="C4" s="100" t="str">
         <v>1,363 seasons
 (216 coaches)</v>
       </c>
-      <c r="D4" s="106" t="str">
+      <c r="D4" s="100" t="str">
         <v>320 seasons
 (54 coaches)</v>
       </c>
@@ -13726,14 +14461,14 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="110" t="str">
+      <c r="B5" s="104" t="str">
         <v>New Coaches in Modern Era</v>
       </c>
-      <c r="C5" s="107" t="str">
+      <c r="C5" s="101" t="str">
         <v>1,652 seasons
 (pre-2020 + 80% of 2020-2024)</v>
       </c>
-      <c r="D5" s="107" t="str">
+      <c r="D5" s="101" t="str">
         <v>31 seasons
 (11 new coaches, 2020-2024)</v>
       </c>
@@ -13752,39 +14487,39 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C7" s="20" t="s">
-        <v>937</v>
+        <v>902</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>938</v>
+        <v>903</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>939</v>
+        <v>904</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>940</v>
+        <v>905</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>941</v>
+        <v>906</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>942</v>
+        <v>907</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>943</v>
+        <v>908</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B8" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>944</v>
+        <v>909</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>947</v>
+        <v>912</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>950</v>
+        <v>915</v>
       </c>
       <c r="F8" s="20">
         <v>0.82399999999999995</v>
@@ -13801,16 +14536,16 @@
     </row>
     <row r="9" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>945</v>
+        <v>910</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>948</v>
+        <v>913</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>951</v>
+        <v>916</v>
       </c>
       <c r="F9" s="20">
         <v>0.81599999999999995</v>
@@ -13827,16 +14562,16 @@
     </row>
     <row r="10" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>946</v>
+        <v>911</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>949</v>
+        <v>914</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>952</v>
+        <v>917</v>
       </c>
       <c r="F10" s="20">
         <v>0.81100000000000005</v>
